--- a/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
+++ b/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="monthly" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="annual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="data_dictionary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10165,4 +10166,958 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>column_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>original_column</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>source_section</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>資料區塊名稱</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>例如：全國、台電、民營電廠、自用發電設備</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>roc_period</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>民國年/月期間</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>各區塊第一欄</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>例如：114年、01月、115年01-03月</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>西元期間</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Column29 / Column26 / Column20 等</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>monthly 為 YYYY/MM；annual 為 YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>total_gwh</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>發電量總計</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>total_share_pct</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>發電量總計占比</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>全國區塊通常沒有此欄；台電、民營電廠等區塊可能有</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pumped_storage_gwh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>抽蓄水力發電量</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pumped_storage_share_pct</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>抽蓄水力發電占比</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>thermal_total_gwh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>火力發電合計</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>thermal_total_share_pct</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>火力發電合計占比</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>coal_gwh</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>燃煤發電量</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>coal_share_pct</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>燃煤發電占比</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>oil_gwh</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>燃油發電量</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>民營電廠區塊可能沒有此欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>oil_share_pct</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>燃油發電占比</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>民營電廠區塊可能沒有此欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lng_gwh</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>燃氣發電量</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>原始表頭為燃氣 / LNG-Fired</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>lng_share_pct</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>燃氣發電占比</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>原始表頭為燃氣 / LNG-Fired</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nuclear_gwh</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>核能發電量</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nuclear_share_pct</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>核能發電占比</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>renewable_total_gwh</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>再生能源發電合計</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>renewable_total_share_pct</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>再生能源發電合計占比</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>hydro_gwh</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>慣常水力發電量</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>hydro_share_pct</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>慣常水力發電占比</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>geothermal_gwh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>地熱發電量</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>geothermal_share_pct</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>地熱發電占比</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>solar_pv_gwh</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>太陽光電發電量</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>solar_pv_share_pct</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>太陽光電發電占比</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>wind_gwh</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>風力發電量</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>原始資料註記：風力統計自 111 年 1 月起納入併聯試運轉發電量，部分月份可能波動較大</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wind_share_pct</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>風力發電占比</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>原始資料註記：風力統計自 111 年 1 月起納入併聯試運轉發電量，部分月份可能波動較大</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>biomass_gwh</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>生質能發電量</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>部分區塊可能沒有此欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>biomass_share_pct</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>生質能發電占比</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>部分區塊可能沒有此欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>waste_gwh</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>廢棄物發電量</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>部分區塊可能沒有此欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>monthly / annual</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>waste_share_pct</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>廢棄物發電占比</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>部分區塊可能沒有此欄</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
+++ b/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE46"/>
+  <dimension ref="A1:AE61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4668,6 +4668,1401 @@
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
         <v>22.09789089393907</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>01月</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2025/01</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3274.882194</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>2314.315224</v>
+      </c>
+      <c r="H47" t="n">
+        <v>10.77627053090561</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2147.105685</v>
+      </c>
+      <c r="J47" t="n">
+        <v>9.997683755462953</v>
+      </c>
+      <c r="K47" t="n">
+        <v>50.385481</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.234612626860465</v>
+      </c>
+      <c r="M47" t="n">
+        <v>116.824058</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.543974148582193</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="n">
+        <v>960.56697</v>
+      </c>
+      <c r="R47" t="n">
+        <v>4.472739678859018</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.281417</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.001310377122592</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.7950159999999999</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.003701875787513</v>
+      </c>
+      <c r="W47" t="n">
+        <v>572.542682</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.665961303688967</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.011636</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>5.4181333034e-05</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>19.233884</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.089559769211481</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>367.702335</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.712152171715431</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>15.24901020976463</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>02月</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2025/02</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3114.775459</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>2112.103544</v>
+      </c>
+      <c r="H48" t="n">
+        <v>10.53140152419157</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1955.281599</v>
+      </c>
+      <c r="J48" t="n">
+        <v>9.749453652700439</v>
+      </c>
+      <c r="K48" t="n">
+        <v>44.475244</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.221763110895283</v>
+      </c>
+      <c r="M48" t="n">
+        <v>112.346701</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.560184760595854</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="n">
+        <v>1002.671915</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4.999537339867786</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.531251</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.002648931491556</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.712547</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.003552912253367</v>
+      </c>
+      <c r="W48" t="n">
+        <v>663.597271</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.308838400045205</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.117873</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.000587740073344</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>23.103078</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.115196904789019</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>314.609895</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.568712451215295</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>15.53093886405936</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>03月</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3804.011423</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>2652.57423</v>
+      </c>
+      <c r="H49" t="n">
+        <v>11.956049303451</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2464.210091</v>
+      </c>
+      <c r="J49" t="n">
+        <v>11.10702841369965</v>
+      </c>
+      <c r="K49" t="n">
+        <v>55.320727</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.249349229150414</v>
+      </c>
+      <c r="M49" t="n">
+        <v>133.043412</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.599671660600934</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="n">
+        <v>1151.437193</v>
+      </c>
+      <c r="R49" t="n">
+        <v>5.189916909256569</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.763782</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.003442623827756</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.756781</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.003411067952626</v>
+      </c>
+      <c r="W49" t="n">
+        <v>808.378154</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.643633778745075</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.009842999999999999</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>4.4365730453e-05</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>24.704981</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.111353705972187</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>316.823652</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.428031367028474</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>17.14596621270757</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>04月</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025/04</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3868.855109</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>2655.303323</v>
+      </c>
+      <c r="H50" t="n">
+        <v>11.88431075794438</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2474.767863</v>
+      </c>
+      <c r="J50" t="n">
+        <v>11.07629026142183</v>
+      </c>
+      <c r="K50" t="n">
+        <v>55.192155</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.247022897813258</v>
+      </c>
+      <c r="M50" t="n">
+        <v>125.343305</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.560997598709292</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="n">
+        <v>1213.551786</v>
+      </c>
+      <c r="R50" t="n">
+        <v>5.431479869270822</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.365019</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.001633711369612</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.69015</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.003088896473164</v>
+      </c>
+      <c r="W50" t="n">
+        <v>903.278927</v>
+      </c>
+      <c r="X50" t="n">
+        <v>4.04279517770579</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.0007286421007480001</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>21.545239</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.09642978013558701</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>287.509651</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.286803661485922</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>17.3157906272152</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>05月</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2025/05</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4440.82781</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>3006.064946</v>
+      </c>
+      <c r="H51" t="n">
+        <v>12.0451217725418</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2815.838541</v>
+      </c>
+      <c r="J51" t="n">
+        <v>11.28289598775736</v>
+      </c>
+      <c r="K51" t="n">
+        <v>66.29382699999999</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.265635384905892</v>
+      </c>
+      <c r="M51" t="n">
+        <v>123.932578</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.496590399878551</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="n">
+        <v>1434.762864</v>
+      </c>
+      <c r="R51" t="n">
+        <v>5.749008661505091</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.43495</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.005749758504223</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.001510656436585</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1078.172642</v>
+      </c>
+      <c r="X51" t="n">
+        <v>4.320173049485777</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.109295</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.000437938503585</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>23.469241</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.094039839734764</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>331.199726</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.327097418840158</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>17.79413043404689</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>06月</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4387.736736</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>2905.62233</v>
+      </c>
+      <c r="H52" t="n">
+        <v>11.16859422334506</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2702.092964</v>
+      </c>
+      <c r="J52" t="n">
+        <v>10.38627063024799</v>
+      </c>
+      <c r="K52" t="n">
+        <v>65.259513</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.250843687558703</v>
+      </c>
+      <c r="M52" t="n">
+        <v>138.269853</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.531479905538367</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="n">
+        <v>1482.114406</v>
+      </c>
+      <c r="R52" t="n">
+        <v>5.696932537405196</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.763989</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.002936611218878</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.233366</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.00474079657244</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1150.395974</v>
+      </c>
+      <c r="X52" t="n">
+        <v>4.421877439858406</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.125543</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.000482560589552</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>21.761918</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.083648184127119</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>307.833616</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.183246945038801</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>16.86552676075026</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>07月</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2025/07</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4424.262609</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>3004.244826</v>
+      </c>
+      <c r="H53" t="n">
+        <v>11.09847596400605</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2792.624691</v>
+      </c>
+      <c r="J53" t="n">
+        <v>10.31669514458983</v>
+      </c>
+      <c r="K53" t="n">
+        <v>56.537753</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.208865431771376</v>
+      </c>
+      <c r="M53" t="n">
+        <v>155.082382</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.572915387644843</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="n">
+        <v>1420.017783</v>
+      </c>
+      <c r="R53" t="n">
+        <v>5.245921736035858</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.73847</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.002728103739818</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.477957</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.001765699729403</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1066.792403</v>
+      </c>
+      <c r="X53" t="n">
+        <v>3.941013642035231</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.054869</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.000202700616274</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>24.134056</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.089157593985643</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>327.820028</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.211053995929489</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>16.34439770004191</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>08月</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025/08</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4320.852279</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>2873.00268</v>
+      </c>
+      <c r="H54" t="n">
+        <v>10.59946960724146</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2676.794533</v>
+      </c>
+      <c r="J54" t="n">
+        <v>9.875592005143416</v>
+      </c>
+      <c r="K54" t="n">
+        <v>71.82566300000001</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.264988939024751</v>
+      </c>
+      <c r="M54" t="n">
+        <v>124.382484</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.458888663073296</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="n">
+        <v>1447.849599</v>
+      </c>
+      <c r="R54" t="n">
+        <v>5.34160233378454</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1.972862</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.007278549008622</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.496823</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.0018329465285</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1080.641706</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3.986849368015404</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.071462</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.000263647264357</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>16.764012</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.06184805775727</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>347.902734</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.283529765210387</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>15.941071941026</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>09月</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4489.613453</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>3034.484122</v>
+      </c>
+      <c r="H55" t="n">
+        <v>11.38255901629311</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2794.142749</v>
+      </c>
+      <c r="J55" t="n">
+        <v>10.48102196675128</v>
+      </c>
+      <c r="K55" t="n">
+        <v>94.357365</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.353940977297495</v>
+      </c>
+      <c r="M55" t="n">
+        <v>145.984008</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.547596072244337</v>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="n">
+        <v>1455.129331</v>
+      </c>
+      <c r="R55" t="n">
+        <v>5.45829037837576</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.991319</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.003718505870459</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.46002</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.001725566715183</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1102.531844</v>
+      </c>
+      <c r="X55" t="n">
+        <v>4.135672910821205</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.046212</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.000173344395987</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>23.340597</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.08755218750425001</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>327.759339</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.229447863068674</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>16.84084939466887</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2025/10</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4463.272802</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>3056.724701</v>
+      </c>
+      <c r="H56" t="n">
+        <v>11.75873084940232</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2851.846223</v>
+      </c>
+      <c r="J56" t="n">
+        <v>10.97059612505208</v>
+      </c>
+      <c r="K56" t="n">
+        <v>71.49725100000001</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.275038485051049</v>
+      </c>
+      <c r="M56" t="n">
+        <v>133.381227</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.513096239299187</v>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="n">
+        <v>1406.548101</v>
+      </c>
+      <c r="R56" t="n">
+        <v>5.410765497130369</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1.664189</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.006401868813091</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.556748</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.002141720476431</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1067.243002</v>
+      </c>
+      <c r="X56" t="n">
+        <v>4.105513070025778</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.294876</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.001134340791899</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>25.305643</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.097346759723149</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>311.483643</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.198227737300022</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>17.16949634653268</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025/11</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3697.633645</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>2525.400691</v>
+      </c>
+      <c r="H57" t="n">
+        <v>11.21395296050141</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2355.142378</v>
+      </c>
+      <c r="J57" t="n">
+        <v>10.4579269089047</v>
+      </c>
+      <c r="K57" t="n">
+        <v>58.359945</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.259145283494915</v>
+      </c>
+      <c r="M57" t="n">
+        <v>111.898368</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.496880768101792</v>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="n">
+        <v>1172.232954</v>
+      </c>
+      <c r="R57" t="n">
+        <v>5.205259209658469</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.606897</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.007135369620587</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.179824</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.000798502148335</v>
+      </c>
+      <c r="W57" t="n">
+        <v>877.21548</v>
+      </c>
+      <c r="X57" t="n">
+        <v>3.8952444909043</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.50652</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.002249184247789</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>21.978321</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.097593961513967</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>270.745912</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.20223770122349</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>16.41921217015987</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>3649.753787</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>2518.201713</v>
+      </c>
+      <c r="H58" t="n">
+        <v>11.16733837026001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2380.281352</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10.55571010732767</v>
+      </c>
+      <c r="K58" t="n">
+        <v>34.638659</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.153610262334474</v>
+      </c>
+      <c r="M58" t="n">
+        <v>103.281702</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.458018000597857</v>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="n">
+        <v>1131.552074</v>
+      </c>
+      <c r="R58" t="n">
+        <v>5.018035222791342</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.019625</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.008956326111449</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0.051883</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.000230082845895</v>
+      </c>
+      <c r="W58" t="n">
+        <v>774.519618</v>
+      </c>
+      <c r="X58" t="n">
+        <v>3.434721930320013</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.5146500000000001</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.002282291630009</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>23.957828</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.106244535738067</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>330.48847</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.465600056145908</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>16.18537359305135</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>01月</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026/01</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3675.474356</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>2571.075815</v>
+      </c>
+      <c r="H59" t="n">
+        <v>11.36493762338099</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2354.471203</v>
+      </c>
+      <c r="J59" t="n">
+        <v>10.40747931353467</v>
+      </c>
+      <c r="K59" t="n">
+        <v>35.662962</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.15764114625885</v>
+      </c>
+      <c r="M59" t="n">
+        <v>180.94165</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.799817163587467</v>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="n">
+        <v>1104.398541</v>
+      </c>
+      <c r="R59" t="n">
+        <v>4.881777680996924</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.833322</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.008103841221645</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0.029316</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.000129585642486</v>
+      </c>
+      <c r="W59" t="n">
+        <v>737.680707</v>
+      </c>
+      <c r="X59" t="n">
+        <v>3.260773242124947</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.393627</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.001739951142545</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>25.320527</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.111924435781811</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>339.141042</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.49910662508349</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>16.24671530437791</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>02月</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>3230.387095</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>2101.863921</v>
+      </c>
+      <c r="H60" t="n">
+        <v>10.87143920719302</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1938.225877</v>
+      </c>
+      <c r="J60" t="n">
+        <v>10.0250566086071</v>
+      </c>
+      <c r="K60" t="n">
+        <v>46.59655</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.241010636097183</v>
+      </c>
+      <c r="M60" t="n">
+        <v>117.041494</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.60537196248874</v>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="n">
+        <v>1128.523174</v>
+      </c>
+      <c r="R60" t="n">
+        <v>5.837043472449192</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1.157865</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.005988807758614</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.021566</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.00011154549807</v>
+      </c>
+      <c r="W60" t="n">
+        <v>768.270438</v>
+      </c>
+      <c r="X60" t="n">
+        <v>3.973713653844366</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.810688</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.00936539436189</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>24.076535</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.124530700564014</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>333.186082</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.723333370422237</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>16.70848267964222</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>03月</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>3851.676032</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>2449.7594</v>
+      </c>
+      <c r="H61" t="n">
+        <v>10.75514068361922</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2236.407344</v>
+      </c>
+      <c r="J61" t="n">
+        <v>9.818464462509745</v>
+      </c>
+      <c r="K61" t="n">
+        <v>56.198143</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.246725835248617</v>
+      </c>
+      <c r="M61" t="n">
+        <v>157.153913</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.689950385860854</v>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="n">
+        <v>1401.916632</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6.1548128374834</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1.754802</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.007704079993283</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.192692</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.000845972697812</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1049.808904</v>
+      </c>
+      <c r="X61" t="n">
+        <v>4.608959742510265</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>3.365258</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.014774439982422</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>28.368082</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.124543950248521</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>318.426894</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>1.397984652051097</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>16.90995352110262</v>
       </c>
     </row>
   </sheetData>
@@ -4681,7 +6076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE61"/>
+  <dimension ref="A1:AE81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10163,6 +11558,1818 @@
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>96年</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>44320.492556</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>40842.595465</v>
+      </c>
+      <c r="H62" t="n">
+        <v>16.79959252521901</v>
+      </c>
+      <c r="I62" t="n">
+        <v>35462.458016</v>
+      </c>
+      <c r="J62" t="n">
+        <v>14.58660591543497</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4625.381745</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1.902536499086481</v>
+      </c>
+      <c r="M62" t="n">
+        <v>754.755704</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.310450110697558</v>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="n">
+        <v>3477.897091</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.430547038165429</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.000896689137603</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>10.169579</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.004183005056557</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>302.267458</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.124330250568559</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>3163.280054</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.30113709340271</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>18.23013956338444</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>97年</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>39329.673308</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>35954.900916</v>
+      </c>
+      <c r="H63" t="n">
+        <v>15.08774293632021</v>
+      </c>
+      <c r="I63" t="n">
+        <v>31622.452589</v>
+      </c>
+      <c r="J63" t="n">
+        <v>13.26971910709647</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3592.360907</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.507461194954447</v>
+      </c>
+      <c r="M63" t="n">
+        <v>740.08742</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.310562634269295</v>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="n">
+        <v>3374.772392</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.416154599842826</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>4.376857</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0.001836659025686</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>9.179506999999999</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.003851993424254</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>272.488611</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.114344303866888</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>3088.727417</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.296121643525997</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>16.50389753616303</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>98年</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>39735.146676</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>36452.366348</v>
+      </c>
+      <c r="H64" t="n">
+        <v>15.84629477194343</v>
+      </c>
+      <c r="I64" t="n">
+        <v>32456.752194</v>
+      </c>
+      <c r="J64" t="n">
+        <v>14.10935185101541</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3276.373741</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.424280212354159</v>
+      </c>
+      <c r="M64" t="n">
+        <v>719.240413</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.312662708573861</v>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="n">
+        <v>3282.780328</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.427065235008516</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>9.014407</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.003918674281734</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>8.277022000000001</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.003598123896641</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>229.349499</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.099701065556501</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>3036.1394</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.319847371273639</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>17.27336000695195</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>99年</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>40627.477023</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>37201.720978</v>
+      </c>
+      <c r="H65" t="n">
+        <v>15.05783679742706</v>
+      </c>
+      <c r="I65" t="n">
+        <v>33380.473026</v>
+      </c>
+      <c r="J65" t="n">
+        <v>13.51114146960216</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2876.170908</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1.16416421056927</v>
+      </c>
+      <c r="M65" t="n">
+        <v>945.077044</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.382531117255637</v>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="n">
+        <v>3425.756045</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.386615298359846</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>17.866793</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0.007231795895854</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>10.297327</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.004167964958058</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>270.037639</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.109300929912064</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>3127.554286</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.26591460759387</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>16.44445209578691</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>100年</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>39819.769008</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>36327.299306</v>
+      </c>
+      <c r="H66" t="n">
+        <v>14.40604728591645</v>
+      </c>
+      <c r="I66" t="n">
+        <v>33345.621161</v>
+      </c>
+      <c r="J66" t="n">
+        <v>13.22362532863213</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2180.132625</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.864559003430563</v>
+      </c>
+      <c r="M66" t="n">
+        <v>801.54552</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.317862953853751</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="n">
+        <v>3492.469702</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.384982771436924</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>52.97875</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.021009389418681</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>6.455651</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.002560069571481</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>236.091082</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.093624886959693</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>3196.944219</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.267788425487068</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>15.79103005735337</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>101年</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>37564.303435</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>33989.239841</v>
+      </c>
+      <c r="H67" t="n">
+        <v>13.57541834574612</v>
+      </c>
+      <c r="I67" t="n">
+        <v>31256.037848</v>
+      </c>
+      <c r="J67" t="n">
+        <v>12.48376814550703</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1963.403504</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.78419005758852</v>
+      </c>
+      <c r="M67" t="n">
+        <v>769.798489</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.307460142650568</v>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="n">
+        <v>3575.063594</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.427892595663557</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>146.661869</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.058577250811074</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>8.590303</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.003430996323756</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>242.070117</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.09668363054459</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>3177.741305</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.269200717984137</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>15.00331094140968</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>102年</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>40531.04884</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>36750.235732</v>
+      </c>
+      <c r="H68" t="n">
+        <v>14.56373032967891</v>
+      </c>
+      <c r="I68" t="n">
+        <v>34558.428923</v>
+      </c>
+      <c r="J68" t="n">
+        <v>13.69514043725449</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1542.876305</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.611425586544083</v>
+      </c>
+      <c r="M68" t="n">
+        <v>648.930504</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.257164305880339</v>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="n">
+        <v>3780.813108</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.498296308447396</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>298.522475</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.118301304376741</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>8.138297</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.003225121158818</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>228.480687</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.090544483449676</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>3245.671649</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.28622539946216</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>16.06202663812631</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>103年</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>42242.661118</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>38171.717375</v>
+      </c>
+      <c r="H69" t="n">
+        <v>14.6834665021244</v>
+      </c>
+      <c r="I69" t="n">
+        <v>36170.346577</v>
+      </c>
+      <c r="J69" t="n">
+        <v>13.91360171500823</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1410.354528</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.542519302041423</v>
+      </c>
+      <c r="M69" t="n">
+        <v>591.01627</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.227345485074747</v>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="n">
+        <v>4070.943743</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.565964808319642</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>485.96358</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0.186934998970097</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>7.022892</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.002701487030751</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>252.466956</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.09711614635780599</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>3325.490315</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.279212175960988</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>16.24943131044403</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>104年</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>40144.929102</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>35707.007673</v>
+      </c>
+      <c r="H70" t="n">
+        <v>13.83231834040563</v>
+      </c>
+      <c r="I70" t="n">
+        <v>33947.36211</v>
+      </c>
+      <c r="J70" t="n">
+        <v>13.15066005594224</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1301.365281</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.504127901413449</v>
+      </c>
+      <c r="M70" t="n">
+        <v>458.280282</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.177530383049941</v>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="n">
+        <v>4437.921429</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.71917911850266</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>795.19538</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0.308045853063657</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>9.543279</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.003696912223735</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>248.990692</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.096454974527204</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>3384.192078</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.310981378688065</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>15.55149745890829</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>105年</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>39536.035063</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>34874.061046</v>
+      </c>
+      <c r="H71" t="n">
+        <v>13.20448693055111</v>
+      </c>
+      <c r="I71" t="n">
+        <v>33043.335311</v>
+      </c>
+      <c r="J71" t="n">
+        <v>12.51131288324572</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1443.345396</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.546498883299372</v>
+      </c>
+      <c r="M71" t="n">
+        <v>387.380339</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.146675164006019</v>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="n">
+        <v>4661.974017</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.765179423665259</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1049.809465</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.397493006102062</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>7.557081</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.002861363841911</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>208.055706</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.078776855012092</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>3396.551765</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.286048198709195</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>14.96966635421636</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>106年</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>38845.440602</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>33730.858383</v>
+      </c>
+      <c r="H72" t="n">
+        <v>12.48105782393267</v>
+      </c>
+      <c r="I72" t="n">
+        <v>32129.538755</v>
+      </c>
+      <c r="J72" t="n">
+        <v>11.88853916802621</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1121.402977</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.414940386068598</v>
+      </c>
+      <c r="M72" t="n">
+        <v>479.916651</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.177578269837863</v>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>5114.582219</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.892492497397257</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1573.540799</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0.582239961925615</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>8.455360000000001</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.003128643685373</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>191.58537</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.070890223250134</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>3341.00069</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1.236233668536136</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>14.37355032132993</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>107年</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>43518.804719</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>37185.489185</v>
+      </c>
+      <c r="H73" t="n">
+        <v>13.49759722169597</v>
+      </c>
+      <c r="I73" t="n">
+        <v>35284.464917</v>
+      </c>
+      <c r="J73" t="n">
+        <v>12.80756300564796</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1420.763067</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.515708897371803</v>
+      </c>
+      <c r="M73" t="n">
+        <v>480.261201</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.174325318676212</v>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="n">
+        <v>6333.315534</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2.298868295924567</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0.001473</v>
+      </c>
+      <c r="V73" t="n">
+        <v>5.34669871e-07</v>
+      </c>
+      <c r="W73" t="n">
+        <v>2545.113281</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.923825790743786</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>29.954504</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.010872892594103</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>191.649309</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.06956490925341501</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>3566.596967</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.294604168663392</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>15.79646551762054</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>108年</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>43616.173778</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>36097.472812</v>
+      </c>
+      <c r="H74" t="n">
+        <v>13.16747499187828</v>
+      </c>
+      <c r="I74" t="n">
+        <v>34352.417178</v>
+      </c>
+      <c r="J74" t="n">
+        <v>12.53092138770207</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1291.697271</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.471179564329937</v>
+      </c>
+      <c r="M74" t="n">
+        <v>453.358363</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.165374039846271</v>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="n">
+        <v>7518.700966</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2.742638174612167</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.756709</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.000276028931042</v>
+      </c>
+      <c r="W74" t="n">
+        <v>3677.271241</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.341378587814163</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>29.291007</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.010684642777298</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>176.520869</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.064390494597988</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>3634.86114</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.325908420491677</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>15.91011316649044</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>109年</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>44222.155853</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>35124.056457</v>
+      </c>
+      <c r="H75" t="n">
+        <v>12.53659277063186</v>
+      </c>
+      <c r="I75" t="n">
+        <v>33442.050817</v>
+      </c>
+      <c r="J75" t="n">
+        <v>11.93624583256105</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1282.052978</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.457594529698994</v>
+      </c>
+      <c r="M75" t="n">
+        <v>399.952662</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.14275240837181</v>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="n">
+        <v>9098.099396</v>
+      </c>
+      <c r="R75" t="n">
+        <v>3.247323305439353</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.311488</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.000111177312726</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1.911729</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.000682340548853</v>
+      </c>
+      <c r="W75" t="n">
+        <v>5292.427913</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.888990629383387</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>21.950039</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.007834479499238999</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>211.75387</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.07557988181249101</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3569.744357</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.274124796882656</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>15.78391607607121</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>110年</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>46978.210455</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>36852.557037</v>
+      </c>
+      <c r="H76" t="n">
+        <v>12.64611770110652</v>
+      </c>
+      <c r="I76" t="n">
+        <v>35103.489988</v>
+      </c>
+      <c r="J76" t="n">
+        <v>12.0459176187466</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1273.663391</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.437063217567376</v>
+      </c>
+      <c r="M76" t="n">
+        <v>475.403658</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.163136864792544</v>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="n">
+        <v>10125.653418</v>
+      </c>
+      <c r="R76" t="n">
+        <v>3.474662688835322</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1.180677</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.000405154526835</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.007435</v>
+      </c>
+      <c r="V76" t="n">
+        <v>2.551353086e-06</v>
+      </c>
+      <c r="W76" t="n">
+        <v>6311.701189</v>
+      </c>
+      <c r="X76" t="n">
+        <v>2.165888137698833</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>6.542752</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.002245174243895</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>201.707471</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.06921680948482101</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>3604.513894</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1.236904861527853</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>16.12078038994184</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>111年</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>41748.685006</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>30070.687503</v>
+      </c>
+      <c r="H77" t="n">
+        <v>10.42646010222948</v>
+      </c>
+      <c r="I77" t="n">
+        <v>28261.383388</v>
+      </c>
+      <c r="J77" t="n">
+        <v>9.799117040453288</v>
+      </c>
+      <c r="K77" t="n">
+        <v>863.397658</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.299367323497252</v>
+      </c>
+      <c r="M77" t="n">
+        <v>945.906457</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.327975738278941</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="n">
+        <v>11677.997503</v>
+      </c>
+      <c r="R77" t="n">
+        <v>4.049131734245105</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5.985916</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.002075506732032</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2.18822</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.000758725204491</v>
+      </c>
+      <c r="W77" t="n">
+        <v>7893.925038</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2.737073917930413</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>6.473741</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.00224465111554</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>164.296272</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.056966722985038</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>3605.128316</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1.250012210277591</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>14.47559183647459</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>112年</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>44825.996185</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>31842.678431</v>
+      </c>
+      <c r="H78" t="n">
+        <v>11.25901084432208</v>
+      </c>
+      <c r="I78" t="n">
+        <v>30048.534422</v>
+      </c>
+      <c r="J78" t="n">
+        <v>10.62463308940494</v>
+      </c>
+      <c r="K78" t="n">
+        <v>629.764006</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.222673472279733</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1164.380003</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.411704282637416</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="n">
+        <v>12983.317754</v>
+      </c>
+      <c r="R78" t="n">
+        <v>4.590672725735741</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5.128676</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.001813409598258</v>
+      </c>
+      <c r="U78" t="n">
+        <v>5.313323</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0.001878697528728</v>
+      </c>
+      <c r="W78" t="n">
+        <v>9111.246664</v>
+      </c>
+      <c r="X78" t="n">
+        <v>3.221576514599995</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0.408266</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.000144355674455</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>244.180945</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.086338085965009</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>3617.03988</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1.278921662369296</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>15.84968357005783</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>113年</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>46192.637039</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>32061.656518</v>
+      </c>
+      <c r="H79" t="n">
+        <v>11.0899447153641</v>
+      </c>
+      <c r="I79" t="n">
+        <v>29926.878767</v>
+      </c>
+      <c r="J79" t="n">
+        <v>10.35153722775072</v>
+      </c>
+      <c r="K79" t="n">
+        <v>649.025075</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.224494083660155</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1485.752676</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.5139134039532181</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="n">
+        <v>14130.980521</v>
+      </c>
+      <c r="R79" t="n">
+        <v>4.887825825961179</v>
+      </c>
+      <c r="S79" t="n">
+        <v>4.103145</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.001419254528648</v>
+      </c>
+      <c r="U79" t="n">
+        <v>9.725549000000001</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.003364012108233</v>
+      </c>
+      <c r="W79" t="n">
+        <v>10238.901328</v>
+      </c>
+      <c r="X79" t="n">
+        <v>3.541577760021216</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>2.276528</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.000787438092876</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>237.716117</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.08222465342678</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>3638.257854</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.258452707783426</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>15.97777054132528</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>114年</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>47936.477306</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>32658.04233</v>
+      </c>
+      <c r="H80" t="n">
+        <v>11.30304187047812</v>
+      </c>
+      <c r="I80" t="n">
+        <v>30410.128669</v>
+      </c>
+      <c r="J80" t="n">
+        <v>10.52503252212957</v>
+      </c>
+      <c r="K80" t="n">
+        <v>724.143583</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.250628165527491</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1523.770078</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.5273811828210619</v>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="n">
+        <v>15278.434976</v>
+      </c>
+      <c r="R80" t="n">
+        <v>5.28791004996855</v>
+      </c>
+      <c r="S80" t="n">
+        <v>13.13377</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.004545635366847</v>
+      </c>
+      <c r="U80" t="n">
+        <v>6.788125</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.002349389480292</v>
+      </c>
+      <c r="W80" t="n">
+        <v>11145.309703</v>
+      </c>
+      <c r="X80" t="n">
+        <v>3.857423569958825</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>2.025579</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.000701058686176</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>269.298798</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.09320508433131899</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>3841.879001</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>1.329685312145091</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>16.59095192044667</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>115年</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10217,19 +13424,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>source_section</t>
+          <t>biomass_gwh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>資料區塊名稱</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>生質能</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>例如：全國、台電、民營電廠、自用發電設備</t>
+          <t>部分區塊可能沒有此欄</t>
         </is>
       </c>
     </row>
@@ -10241,23 +13456,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>roc_period</t>
+          <t>biomass_share_pct</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>民國年/月期間</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>生質能占比</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>各區塊第一欄</t>
+          <t>依 source_section 而異</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>例如：114年、01月、115年01-03月</t>
+          <t>部分區塊可能沒有此欄</t>
         </is>
       </c>
     </row>
@@ -10269,25 +13488,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>period</t>
+          <t>coal_gwh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>西元期間</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>燃煤</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Column29 / Column26 / Column20 等</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>monthly 為 YYYY/MM；annual 為 YYYY</t>
-        </is>
-      </c>
+          <t>依 source_section 而異</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10297,17 +13516,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>total_gwh</t>
+          <t>coal_share_pct</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>發電量總計</t>
+          <t>燃煤占比</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10325,17 +13544,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>total_share_pct</t>
+          <t>geothermal_gwh</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>發電量總計占比</t>
+          <t>地熱</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GWh</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -10343,11 +13562,7 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>全國區塊通常沒有此欄；台電、民營電廠等區塊可能有</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10357,17 +13572,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pumped_storage_gwh</t>
+          <t>geothermal_share_pct</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>抽蓄水力發電量</t>
+          <t>地熱占比</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10385,17 +13600,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pumped_storage_share_pct</t>
+          <t>hydro_gwh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>抽蓄水力發電占比</t>
+          <t>慣常水力</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GWh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -10413,17 +13628,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>thermal_total_gwh</t>
+          <t>hydro_share_pct</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>火力發電合計</t>
+          <t>慣常水力占比</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10441,17 +13656,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>thermal_total_share_pct</t>
+          <t>lng_gwh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>火力發電合計占比</t>
+          <t>燃氣</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GWh</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -10459,7 +13674,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>原始表頭為燃氣 / LNG-Fired</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10469,17 +13688,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>coal_gwh</t>
+          <t>lng_share_pct</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>燃煤發電量</t>
+          <t>燃氣占比</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -10487,7 +13706,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>原始表頭為燃氣 / LNG-Fired</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10497,17 +13720,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>coal_share_pct</t>
+          <t>nuclear_gwh</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>燃煤發電占比</t>
+          <t>核能</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GWh</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10525,17 +13748,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>oil_gwh</t>
+          <t>nuclear_share_pct</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>燃油發電量</t>
+          <t>核能占比</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -10543,11 +13766,7 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>民營電廠區塊可能沒有此欄</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10557,17 +13776,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>oil_share_pct</t>
+          <t>oil_gwh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>燃油發電占比</t>
+          <t>燃油</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GWh</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10577,7 +13796,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>民營電廠區塊可能沒有此欄</t>
+          <t>部分區塊可能沒有此欄</t>
         </is>
       </c>
     </row>
@@ -10589,17 +13808,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lng_gwh</t>
+          <t>oil_share_pct</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>燃氣發電量</t>
+          <t>燃油占比</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10609,7 +13828,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>原始表頭為燃氣 / LNG-Fired</t>
+          <t>部分區塊可能沒有此欄</t>
         </is>
       </c>
     </row>
@@ -10621,27 +13840,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lng_share_pct</t>
+          <t>period</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>燃氣發電占比</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>西元期間</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>依 source_section 而異</t>
+          <t>各區塊 Period 欄位</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>原始表頭為燃氣 / LNG-Fired</t>
+          <t>monthly 為 YYYY/MM；annual 為 YYYY</t>
         </is>
       </c>
     </row>
@@ -10653,12 +13868,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nuclear_gwh</t>
+          <t>pumped_storage_gwh</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>核能發電量</t>
+          <t>抽蓄水力</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10681,12 +13896,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nuclear_share_pct</t>
+          <t>pumped_storage_share_pct</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>核能發電占比</t>
+          <t>抽蓄水力占比</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10714,7 +13929,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>再生能源發電合計</t>
+          <t>再生能源合計</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10742,7 +13957,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>再生能源發電合計占比</t>
+          <t>再生能源合計占比</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -10765,25 +13980,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hydro_gwh</t>
+          <t>roc_period</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>慣常水力發電量</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>GWh</t>
-        </is>
-      </c>
+          <t>民國年/月期間</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>依 source_section 而異</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>各區塊第一欄</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>例如：114年、01月</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10793,17 +14008,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hydro_share_pct</t>
+          <t>solar_pv_gwh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>慣常水力發電占比</t>
+          <t>太陽光電</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GWh</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10821,17 +14036,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>geothermal_gwh</t>
+          <t>solar_pv_share_pct</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>地熱發電量</t>
+          <t>太陽光電占比</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10849,25 +14064,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>geothermal_share_pct</t>
+          <t>source_section</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>地熱發電占比</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>依 source_section 而異</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>資料區塊名稱</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>例如：全國、台電、民營電廠、自用發電設備</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10877,12 +14088,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>solar_pv_gwh</t>
+          <t>thermal_total_gwh</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>太陽光電發電量</t>
+          <t>火力合計</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10905,12 +14116,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>solar_pv_share_pct</t>
+          <t>thermal_total_share_pct</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>太陽光電發電占比</t>
+          <t>火力合計占比</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10933,12 +14144,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wind_gwh</t>
+          <t>total_gwh</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>風力發電量</t>
+          <t>總計</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -10951,11 +14162,7 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>原始資料註記：風力統計自 111 年 1 月起納入併聯試運轉發電量，部分月份可能波動較大</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10965,12 +14172,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wind_share_pct</t>
+          <t>total_share_pct</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>風力發電占比</t>
+          <t>總計占比</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -10985,7 +14192,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>原始資料註記：風力統計自 111 年 1 月起納入併聯試運轉發電量，部分月份可能波動較大</t>
+          <t>部分區塊才有</t>
         </is>
       </c>
     </row>
@@ -10997,12 +14204,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>biomass_gwh</t>
+          <t>waste_gwh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>生質能發電量</t>
+          <t>廢棄物</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -11029,12 +14236,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>biomass_share_pct</t>
+          <t>waste_share_pct</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>生質能發電占比</t>
+          <t>廢棄物占比</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11061,12 +14268,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>waste_gwh</t>
+          <t>wind_gwh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>廢棄物發電量</t>
+          <t>風力</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -11079,11 +14286,7 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>部分區塊可能沒有此欄</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11093,12 +14296,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>waste_share_pct</t>
+          <t>wind_share_pct</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>廢棄物發電占比</t>
+          <t>風力占比</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11111,11 +14314,7 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>部分區塊可能沒有此欄</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
+++ b/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
@@ -13444,7 +13444,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>部分區塊可能沒有此欄</t>
+          <t>3-02 / 3-03 使用</t>
         </is>
       </c>
     </row>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>部分區塊可能沒有此欄</t>
+          <t>3-02 / 3-03 使用</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14076,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>例如：全國、台電、民營電廠、自用發電設備</t>
+          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14286,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3-02 / 3-03 使用</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14314,7 +14318,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3-02 / 3-03 使用</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
+++ b/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
@@ -13942,7 +13942,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3-02 / 3-03 使用</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13970,7 +13974,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3-02 / 3-03 使用</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">

--- a/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
+++ b/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
@@ -14084,7 +14084,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源</t>
+          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源、直轉供及躉售</t>
         </is>
       </c>
     </row>

--- a/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
+++ b/output/zone_monthly_3_02/electricity_generation_3_02.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE65"/>
+  <dimension ref="A1:AE69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,95 +2162,101 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>台電</t>
+          <t>全國</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/05</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12263.785811</v>
+        <v>25268.745874029</v>
       </c>
       <c r="E18" t="n">
-        <v>265.499</v>
+        <v>235.492</v>
       </c>
       <c r="F18" t="n">
-        <v>1.247797291246011</v>
+        <v>0.931949694591043</v>
       </c>
       <c r="G18" t="n">
-        <v>10883.830577</v>
+        <v>21704.081629247</v>
       </c>
       <c r="H18" t="n">
-        <v>51.15203564744542</v>
+        <v>85.89299103899836</v>
       </c>
       <c r="I18" t="n">
-        <v>3544.285128</v>
+        <v>8979.985528880001</v>
       </c>
       <c r="J18" t="n">
-        <v>16.65749920761254</v>
+        <v>35.53791539021156</v>
       </c>
       <c r="K18" t="n">
-        <v>187.107547</v>
+        <v>309.834251898</v>
       </c>
       <c r="L18" t="n">
-        <v>0.879371637250181</v>
+        <v>1.226156032604867</v>
       </c>
       <c r="M18" t="n">
-        <v>7152.437902</v>
+        <v>12414.261848469</v>
       </c>
       <c r="N18" t="n">
-        <v>33.6151648025827</v>
+        <v>49.12891961618195</v>
       </c>
       <c r="O18" t="n">
-        <v>735.41911</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.456336835123871</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>379.037124</v>
+        <v>3329.172244782</v>
       </c>
       <c r="R18" t="n">
-        <v>1.781405943558652</v>
+        <v>13.17505926641059</v>
       </c>
       <c r="S18" t="n">
-        <v>191.043425</v>
+        <v>273.694199</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8978695521465641</v>
+        <v>1.083133291871444</v>
       </c>
       <c r="U18" t="n">
-        <v>0.536648</v>
+        <v>2.242804</v>
       </c>
       <c r="V18" t="n">
-        <v>0.002522148560833</v>
+        <v>0.008875802587040999</v>
       </c>
       <c r="W18" t="n">
-        <v>29.802548</v>
+        <v>1802.03958703</v>
       </c>
       <c r="X18" t="n">
-        <v>0.140066586565785</v>
+        <v>7.131495943699053</v>
       </c>
       <c r="Y18" t="n">
-        <v>157.654503</v>
+        <v>858.8302169999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.74094765628547</v>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="n">
-        <v>57.63757571737396</v>
-      </c>
+        <v>3.39878449560371</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>25.254442649</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.099943395587971</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>367.110995103</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.452826337061364</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2260,89 +2266,89 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12351.214939</v>
+        <v>12263.785811</v>
       </c>
       <c r="E19" t="n">
-        <v>236.422</v>
+        <v>265.499</v>
       </c>
       <c r="F19" t="n">
-        <v>1.176134550919205</v>
+        <v>1.247797291246011</v>
       </c>
       <c r="G19" t="n">
-        <v>10990.725749</v>
+        <v>10883.830577</v>
       </c>
       <c r="H19" t="n">
-        <v>54.67584358932864</v>
+        <v>51.15203564744542</v>
       </c>
       <c r="I19" t="n">
-        <v>3559.221046</v>
+        <v>3544.285128</v>
       </c>
       <c r="J19" t="n">
-        <v>17.70614767897823</v>
+        <v>16.65749920761254</v>
       </c>
       <c r="K19" t="n">
-        <v>226.208042</v>
+        <v>187.107547</v>
       </c>
       <c r="L19" t="n">
-        <v>1.125322913654324</v>
+        <v>0.879371637250181</v>
       </c>
       <c r="M19" t="n">
-        <v>7205.296661</v>
+        <v>7152.437902</v>
       </c>
       <c r="N19" t="n">
-        <v>35.84437299669608</v>
+        <v>33.6151648025827</v>
       </c>
       <c r="O19" t="n">
-        <v>664.17947</v>
+        <v>735.41911</v>
       </c>
       <c r="P19" t="n">
-        <v>3.304110542496914</v>
+        <v>3.456336835123871</v>
       </c>
       <c r="Q19" t="n">
-        <v>459.88772</v>
+        <v>379.037124</v>
       </c>
       <c r="R19" t="n">
-        <v>2.287815165405321</v>
+        <v>1.781405943558652</v>
       </c>
       <c r="S19" t="n">
-        <v>294.752885</v>
+        <v>191.043425</v>
       </c>
       <c r="T19" t="n">
-        <v>1.466314691659892</v>
+        <v>0.8978695521465641</v>
       </c>
       <c r="U19" t="n">
-        <v>0.449882</v>
+        <v>0.536648</v>
       </c>
       <c r="V19" t="n">
-        <v>0.002238039455028</v>
+        <v>0.002522148560833</v>
       </c>
       <c r="W19" t="n">
-        <v>26.550357</v>
+        <v>29.802548</v>
       </c>
       <c r="X19" t="n">
-        <v>0.132080737862549</v>
+        <v>0.140066586565785</v>
       </c>
       <c r="Y19" t="n">
-        <v>138.134596</v>
+        <v>157.654503</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.687181696427853</v>
+        <v>0.74094765628547</v>
       </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>61.44390384815006</v>
+        <v>57.63757571737396</v>
       </c>
     </row>
     <row r="20">
@@ -2353,89 +2359,89 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12873.037762</v>
+        <v>12351.214939</v>
       </c>
       <c r="E20" t="n">
-        <v>248.231</v>
+        <v>236.422</v>
       </c>
       <c r="F20" t="n">
-        <v>1.096510739250082</v>
+        <v>1.176134550919205</v>
       </c>
       <c r="G20" t="n">
-        <v>11369.236988</v>
+        <v>10990.725749</v>
       </c>
       <c r="H20" t="n">
-        <v>50.22132793414706</v>
+        <v>54.67584358932864</v>
       </c>
       <c r="I20" t="n">
-        <v>3699.041664</v>
+        <v>3559.221046</v>
       </c>
       <c r="J20" t="n">
-        <v>16.33977589225155</v>
+        <v>17.70614767897823</v>
       </c>
       <c r="K20" t="n">
-        <v>275.911761</v>
+        <v>226.208042</v>
       </c>
       <c r="L20" t="n">
-        <v>1.218784958453626</v>
+        <v>1.125322913654324</v>
       </c>
       <c r="M20" t="n">
-        <v>7394.283563</v>
+        <v>7205.296661</v>
       </c>
       <c r="N20" t="n">
-        <v>32.66276708344188</v>
+        <v>35.84437299669608</v>
       </c>
       <c r="O20" t="n">
-        <v>734.05373</v>
+        <v>664.17947</v>
       </c>
       <c r="P20" t="n">
-        <v>3.242535372824426</v>
+        <v>3.304110542496914</v>
       </c>
       <c r="Q20" t="n">
-        <v>521.516044</v>
+        <v>459.88772</v>
       </c>
       <c r="R20" t="n">
-        <v>2.303692701303295</v>
+        <v>2.287815165405321</v>
       </c>
       <c r="S20" t="n">
-        <v>376.551169</v>
+        <v>294.752885</v>
       </c>
       <c r="T20" t="n">
-        <v>1.663339392282481</v>
+        <v>1.466314691659892</v>
       </c>
       <c r="U20" t="n">
-        <v>0.473571</v>
+        <v>0.449882</v>
       </c>
       <c r="V20" t="n">
-        <v>0.002091905069461</v>
+        <v>0.002238039455028</v>
       </c>
       <c r="W20" t="n">
-        <v>35.400109</v>
+        <v>26.550357</v>
       </c>
       <c r="X20" t="n">
-        <v>0.156372893349837</v>
+        <v>0.132080737862549</v>
       </c>
       <c r="Y20" t="n">
-        <v>109.091195</v>
+        <v>138.134596</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.481888510601516</v>
+        <v>0.687181696427853</v>
       </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>56.86406674752486</v>
+        <v>61.44390384815006</v>
       </c>
     </row>
     <row r="21">
@@ -2446,89 +2452,89 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13646.591205</v>
+        <v>12873.037762</v>
       </c>
       <c r="E21" t="n">
-        <v>258.513</v>
+        <v>248.231</v>
       </c>
       <c r="F21" t="n">
-        <v>1.145308720835341</v>
+        <v>1.096510739250082</v>
       </c>
       <c r="G21" t="n">
-        <v>12152.295187</v>
+        <v>11369.236988</v>
       </c>
       <c r="H21" t="n">
-        <v>53.8391866398844</v>
+        <v>50.22132793414706</v>
       </c>
       <c r="I21" t="n">
-        <v>4659.960932</v>
+        <v>3699.041664</v>
       </c>
       <c r="J21" t="n">
-        <v>20.64535978527804</v>
+        <v>16.33977589225155</v>
       </c>
       <c r="K21" t="n">
-        <v>294.219304</v>
+        <v>275.911761</v>
       </c>
       <c r="L21" t="n">
-        <v>1.303500925327949</v>
+        <v>1.218784958453626</v>
       </c>
       <c r="M21" t="n">
-        <v>7198.114951</v>
+        <v>7394.283563</v>
       </c>
       <c r="N21" t="n">
-        <v>31.89032592927841</v>
+        <v>32.66276708344188</v>
       </c>
       <c r="O21" t="n">
-        <v>709.11369</v>
+        <v>734.05373</v>
       </c>
       <c r="P21" t="n">
-        <v>3.141637338241126</v>
+        <v>3.242535372824426</v>
       </c>
       <c r="Q21" t="n">
-        <v>526.669328</v>
+        <v>521.516044</v>
       </c>
       <c r="R21" t="n">
-        <v>2.333340970685762</v>
+        <v>2.303692701303295</v>
       </c>
       <c r="S21" t="n">
-        <v>440.912354</v>
+        <v>376.551169</v>
       </c>
       <c r="T21" t="n">
-        <v>1.953405686213997</v>
+        <v>1.663339392282481</v>
       </c>
       <c r="U21" t="n">
-        <v>0.430232</v>
+        <v>0.473571</v>
       </c>
       <c r="V21" t="n">
-        <v>0.00190608774639</v>
+        <v>0.002091905069461</v>
       </c>
       <c r="W21" t="n">
-        <v>36.339937</v>
+        <v>35.400109</v>
       </c>
       <c r="X21" t="n">
-        <v>0.160999434305845</v>
+        <v>0.156372893349837</v>
       </c>
       <c r="Y21" t="n">
-        <v>48.986805</v>
+        <v>109.091195</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.217029762419531</v>
+        <v>0.481888510601516</v>
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>60.45947366964662</v>
+        <v>56.86406674752486</v>
       </c>
     </row>
     <row r="22">
@@ -2539,89 +2545,89 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15253.045053</v>
+        <v>13646.591205</v>
       </c>
       <c r="E22" t="n">
-        <v>270.672</v>
+        <v>258.513</v>
       </c>
       <c r="F22" t="n">
-        <v>1.083350205963959</v>
+        <v>1.145308720835341</v>
       </c>
       <c r="G22" t="n">
-        <v>13905.188622</v>
+        <v>12152.295187</v>
       </c>
       <c r="H22" t="n">
-        <v>55.65477388725616</v>
+        <v>53.8391866398844</v>
       </c>
       <c r="I22" t="n">
-        <v>5151.395587</v>
+        <v>4659.960932</v>
       </c>
       <c r="J22" t="n">
-        <v>20.61818536892726</v>
+        <v>20.64535978527804</v>
       </c>
       <c r="K22" t="n">
-        <v>333.947523</v>
+        <v>294.219304</v>
       </c>
       <c r="L22" t="n">
-        <v>1.336607103147736</v>
+        <v>1.303500925327949</v>
       </c>
       <c r="M22" t="n">
-        <v>8419.845512</v>
+        <v>7198.114951</v>
       </c>
       <c r="N22" t="n">
-        <v>33.69998141518116</v>
+        <v>31.89032592927841</v>
       </c>
       <c r="O22" t="n">
-        <v>394.65834</v>
+        <v>709.11369</v>
       </c>
       <c r="P22" t="n">
-        <v>1.579598901712753</v>
+        <v>3.141637338241126</v>
       </c>
       <c r="Q22" t="n">
-        <v>682.526091</v>
+        <v>526.669328</v>
       </c>
       <c r="R22" t="n">
-        <v>2.731774181520903</v>
+        <v>2.333340970685762</v>
       </c>
       <c r="S22" t="n">
-        <v>604.585834</v>
+        <v>440.912354</v>
       </c>
       <c r="T22" t="n">
-        <v>2.419822470690696</v>
+        <v>1.953405686213997</v>
       </c>
       <c r="U22" t="n">
-        <v>0.456524</v>
+        <v>0.430232</v>
       </c>
       <c r="V22" t="n">
-        <v>0.001827212897631</v>
+        <v>0.00190608774639</v>
       </c>
       <c r="W22" t="n">
-        <v>39.334531</v>
+        <v>36.339937</v>
       </c>
       <c r="X22" t="n">
-        <v>0.157434356935131</v>
+        <v>0.160999434305845</v>
       </c>
       <c r="Y22" t="n">
-        <v>38.149202</v>
+        <v>48.986805</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.152690140997446</v>
+        <v>0.217029762419531</v>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>61.04949717645378</v>
+        <v>60.45947366964662</v>
       </c>
     </row>
     <row r="23">
@@ -2632,89 +2638,89 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15850.916173</v>
+        <v>15253.045053</v>
       </c>
       <c r="E23" t="n">
-        <v>271.262</v>
+        <v>270.672</v>
       </c>
       <c r="F23" t="n">
-        <v>1.041084060021846</v>
+        <v>1.083350205963959</v>
       </c>
       <c r="G23" t="n">
-        <v>14918.49065</v>
+        <v>13905.188622</v>
       </c>
       <c r="H23" t="n">
-        <v>57.25609490197652</v>
+        <v>55.65477388725616</v>
       </c>
       <c r="I23" t="n">
-        <v>5788.05086</v>
+        <v>5151.395587</v>
       </c>
       <c r="J23" t="n">
-        <v>22.21412320539456</v>
+        <v>20.61818536892726</v>
       </c>
       <c r="K23" t="n">
-        <v>369.066441</v>
+        <v>333.947523</v>
       </c>
       <c r="L23" t="n">
-        <v>1.416450475238306</v>
+        <v>1.336607103147736</v>
       </c>
       <c r="M23" t="n">
-        <v>8761.373349</v>
+        <v>8419.845512</v>
       </c>
       <c r="N23" t="n">
-        <v>33.62552122134365</v>
+        <v>33.69998141518116</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>394.65834</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.579598901712753</v>
       </c>
       <c r="Q23" t="n">
-        <v>661.1635230000001</v>
+        <v>682.526091</v>
       </c>
       <c r="R23" t="n">
-        <v>2.537498082529759</v>
+        <v>2.731774181520903</v>
       </c>
       <c r="S23" t="n">
-        <v>592.7672700000001</v>
+        <v>604.585834</v>
       </c>
       <c r="T23" t="n">
-        <v>2.274998179249825</v>
+        <v>2.419822470690696</v>
       </c>
       <c r="U23" t="n">
-        <v>0.390102</v>
+        <v>0.456524</v>
       </c>
       <c r="V23" t="n">
-        <v>0.001497183438825</v>
+        <v>0.001827212897631</v>
       </c>
       <c r="W23" t="n">
-        <v>39.226601</v>
+        <v>39.334531</v>
       </c>
       <c r="X23" t="n">
-        <v>0.150548875367494</v>
+        <v>0.157434356935131</v>
       </c>
       <c r="Y23" t="n">
-        <v>28.77955</v>
+        <v>38.149202</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.110453844473615</v>
+        <v>0.152690140997446</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>60.83467704452811</v>
+        <v>61.04949717645378</v>
       </c>
     </row>
     <row r="24">
@@ -2725,46 +2731,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16742.457426</v>
+        <v>15850.916173</v>
       </c>
       <c r="E24" t="n">
-        <v>239.174</v>
+        <v>271.262</v>
       </c>
       <c r="F24" t="n">
-        <v>0.881263900185288</v>
+        <v>1.041084060021846</v>
       </c>
       <c r="G24" t="n">
-        <v>15767.853561</v>
+        <v>14918.49065</v>
       </c>
       <c r="H24" t="n">
-        <v>58.09845604755259</v>
+        <v>57.25609490197652</v>
       </c>
       <c r="I24" t="n">
-        <v>5751.618597</v>
+        <v>5788.05086</v>
       </c>
       <c r="J24" t="n">
-        <v>21.19249515904928</v>
+        <v>22.21412320539456</v>
       </c>
       <c r="K24" t="n">
-        <v>292.135585</v>
+        <v>369.066441</v>
       </c>
       <c r="L24" t="n">
-        <v>1.07640690468032</v>
+        <v>1.416450475238306</v>
       </c>
       <c r="M24" t="n">
-        <v>9724.099378999999</v>
+        <v>8761.373349</v>
       </c>
       <c r="N24" t="n">
-        <v>35.82955398382298</v>
+        <v>33.62552122134365</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2773,41 +2779,41 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>735.4298649999999</v>
+        <v>661.1635230000001</v>
       </c>
       <c r="R24" t="n">
-        <v>2.709775272992214</v>
+        <v>2.537498082529759</v>
       </c>
       <c r="S24" t="n">
-        <v>658.332578</v>
+        <v>592.7672700000001</v>
       </c>
       <c r="T24" t="n">
-        <v>2.425701519844612</v>
+        <v>2.274998179249825</v>
       </c>
       <c r="U24" t="n">
-        <v>0.028881</v>
+        <v>0.390102</v>
       </c>
       <c r="V24" t="n">
-        <v>0.00010641534072</v>
+        <v>0.001497183438825</v>
       </c>
       <c r="W24" t="n">
-        <v>30.297467</v>
+        <v>39.226601</v>
       </c>
       <c r="X24" t="n">
-        <v>0.111634475043922</v>
+        <v>0.150548875367494</v>
       </c>
       <c r="Y24" t="n">
-        <v>46.770939</v>
+        <v>28.77955</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.17233286276296</v>
+        <v>0.110453844473615</v>
       </c>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>61.68949522073009</v>
+        <v>60.83467704452811</v>
       </c>
     </row>
     <row r="25">
@@ -2818,46 +2824,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17341.7041</v>
+        <v>16742.457426</v>
       </c>
       <c r="E25" t="n">
-        <v>230.909</v>
+        <v>239.174</v>
       </c>
       <c r="F25" t="n">
-        <v>0.851834600910494</v>
+        <v>0.881263900185288</v>
       </c>
       <c r="G25" t="n">
-        <v>16313.1389</v>
+        <v>15767.853561</v>
       </c>
       <c r="H25" t="n">
-        <v>60.17996771229775</v>
+        <v>58.09845604755259</v>
       </c>
       <c r="I25" t="n">
-        <v>5899.511438</v>
+        <v>5751.618597</v>
       </c>
       <c r="J25" t="n">
-        <v>21.76358639704657</v>
+        <v>21.19249515904928</v>
       </c>
       <c r="K25" t="n">
-        <v>319.725351</v>
+        <v>292.135585</v>
       </c>
       <c r="L25" t="n">
-        <v>1.179482466123247</v>
+        <v>1.07640690468032</v>
       </c>
       <c r="M25" t="n">
-        <v>10093.902111</v>
+        <v>9724.099378999999</v>
       </c>
       <c r="N25" t="n">
-        <v>37.23689884912793</v>
+        <v>35.82955398382298</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2866,41 +2872,41 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>797.6562</v>
+        <v>735.4298649999999</v>
       </c>
       <c r="R25" t="n">
-        <v>2.942592756413918</v>
+        <v>2.709775272992214</v>
       </c>
       <c r="S25" t="n">
-        <v>732.547195</v>
+        <v>658.332578</v>
       </c>
       <c r="T25" t="n">
-        <v>2.702402450753012</v>
+        <v>2.425701519844612</v>
       </c>
       <c r="U25" t="n">
-        <v>0.473468</v>
+        <v>0.028881</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001746646621933</v>
+        <v>0.00010641534072</v>
       </c>
       <c r="W25" t="n">
-        <v>38.213027</v>
+        <v>30.297467</v>
       </c>
       <c r="X25" t="n">
-        <v>0.140969726620127</v>
+        <v>0.111634475043922</v>
       </c>
       <c r="Y25" t="n">
-        <v>26.42251</v>
+        <v>46.770939</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.097473932418847</v>
+        <v>0.17233286276296</v>
       </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>63.97439506962216</v>
+        <v>61.68949522073009</v>
       </c>
     </row>
     <row r="26">
@@ -2911,46 +2917,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16923.642225</v>
+        <v>17341.7041</v>
       </c>
       <c r="E26" t="n">
-        <v>300.007</v>
+        <v>230.909</v>
       </c>
       <c r="F26" t="n">
-        <v>1.124635476651676</v>
+        <v>0.851834600910494</v>
       </c>
       <c r="G26" t="n">
-        <v>16057.58676</v>
+        <v>16313.1389</v>
       </c>
       <c r="H26" t="n">
-        <v>60.19503458155393</v>
+        <v>60.17996771229775</v>
       </c>
       <c r="I26" t="n">
-        <v>6008.940234</v>
+        <v>5899.511438</v>
       </c>
       <c r="J26" t="n">
-        <v>22.5256989478113</v>
+        <v>21.76358639704657</v>
       </c>
       <c r="K26" t="n">
-        <v>445.630397</v>
+        <v>319.725351</v>
       </c>
       <c r="L26" t="n">
-        <v>1.670533534019442</v>
+        <v>1.179482466123247</v>
       </c>
       <c r="M26" t="n">
-        <v>9603.016129</v>
+        <v>10093.902111</v>
       </c>
       <c r="N26" t="n">
-        <v>35.99880209972317</v>
+        <v>37.23689884912793</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2959,41 +2965,41 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>566.048465</v>
+        <v>797.6562</v>
       </c>
       <c r="R26" t="n">
-        <v>2.121944438773845</v>
+        <v>2.942592756413918</v>
       </c>
       <c r="S26" t="n">
-        <v>514.107814</v>
+        <v>732.547195</v>
       </c>
       <c r="T26" t="n">
-        <v>1.927234652685575</v>
+        <v>2.702402450753012</v>
       </c>
       <c r="U26" t="n">
-        <v>0.397113</v>
+        <v>0.473468</v>
       </c>
       <c r="V26" t="n">
-        <v>0.00148865649148</v>
+        <v>0.001746646621933</v>
       </c>
       <c r="W26" t="n">
-        <v>37.545736</v>
+        <v>38.213027</v>
       </c>
       <c r="X26" t="n">
-        <v>0.140747604897879</v>
+        <v>0.140969726620127</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.997802</v>
+        <v>26.42251</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.05247352469891</v>
+        <v>0.097473932418847</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>63.44161449697944</v>
+        <v>63.97439506962216</v>
       </c>
     </row>
     <row r="27">
@@ -3004,46 +3010,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15750.531002</v>
+        <v>16923.642225</v>
       </c>
       <c r="E27" t="n">
-        <v>285.357</v>
+        <v>300.007</v>
       </c>
       <c r="F27" t="n">
-        <v>1.096734836560902</v>
+        <v>1.124635476651676</v>
       </c>
       <c r="G27" t="n">
-        <v>14939.779604</v>
+        <v>16057.58676</v>
       </c>
       <c r="H27" t="n">
-        <v>57.41922133414929</v>
+        <v>60.19503458155393</v>
       </c>
       <c r="I27" t="n">
-        <v>4169.276575</v>
+        <v>6008.940234</v>
       </c>
       <c r="J27" t="n">
-        <v>16.02410616546929</v>
+        <v>22.5256989478113</v>
       </c>
       <c r="K27" t="n">
-        <v>372.315853</v>
+        <v>445.630397</v>
       </c>
       <c r="L27" t="n">
-        <v>1.43095058536846</v>
+        <v>1.670533534019442</v>
       </c>
       <c r="M27" t="n">
-        <v>10398.187176</v>
+        <v>9603.016129</v>
       </c>
       <c r="N27" t="n">
-        <v>39.96416458331151</v>
+        <v>35.99880209972317</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3052,41 +3058,41 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>525.394398</v>
+        <v>566.048465</v>
       </c>
       <c r="R27" t="n">
-        <v>2.019289308552247</v>
+        <v>2.121944438773845</v>
       </c>
       <c r="S27" t="n">
-        <v>415.261327</v>
+        <v>514.107814</v>
       </c>
       <c r="T27" t="n">
-        <v>1.596006278442121</v>
+        <v>1.927234652685575</v>
       </c>
       <c r="U27" t="n">
-        <v>0.251632</v>
+        <v>0.397113</v>
       </c>
       <c r="V27" t="n">
-        <v>0.000967116911075</v>
+        <v>0.00148865649148</v>
       </c>
       <c r="W27" t="n">
-        <v>34.68658</v>
+        <v>37.545736</v>
       </c>
       <c r="X27" t="n">
-        <v>0.133313640973085</v>
+        <v>0.140747604897879</v>
       </c>
       <c r="Y27" t="n">
-        <v>75.19485899999999</v>
+        <v>13.997802</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.289002272225966</v>
+        <v>0.05247352469891</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>60.53524547926242</v>
+        <v>63.44161449697944</v>
       </c>
     </row>
     <row r="28">
@@ -3097,46 +3103,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13137.780857</v>
+        <v>15750.531002</v>
       </c>
       <c r="E28" t="n">
-        <v>246.141</v>
+        <v>285.357</v>
       </c>
       <c r="F28" t="n">
-        <v>1.091526151623337</v>
+        <v>1.096734836560902</v>
       </c>
       <c r="G28" t="n">
-        <v>12358.591255</v>
+        <v>14939.779604</v>
       </c>
       <c r="H28" t="n">
-        <v>54.80487018439013</v>
+        <v>57.41922133414929</v>
       </c>
       <c r="I28" t="n">
-        <v>3146.95806</v>
+        <v>4169.276575</v>
       </c>
       <c r="J28" t="n">
-        <v>13.95536306650189</v>
+        <v>16.02410616546929</v>
       </c>
       <c r="K28" t="n">
-        <v>232.819909</v>
+        <v>372.315853</v>
       </c>
       <c r="L28" t="n">
-        <v>1.032453022016102</v>
+        <v>1.43095058536846</v>
       </c>
       <c r="M28" t="n">
-        <v>8978.813286000001</v>
+        <v>10398.187176</v>
       </c>
       <c r="N28" t="n">
-        <v>39.81705409587214</v>
+        <v>39.96416458331151</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3145,41 +3151,41 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>533.048602</v>
+        <v>525.394398</v>
       </c>
       <c r="R28" t="n">
-        <v>2.363834099842203</v>
+        <v>2.019289308552247</v>
       </c>
       <c r="S28" t="n">
-        <v>355.822667</v>
+        <v>415.261327</v>
       </c>
       <c r="T28" t="n">
-        <v>1.577915692106809</v>
+        <v>1.596006278442121</v>
       </c>
       <c r="U28" t="n">
-        <v>2.7e-05</v>
+        <v>0.251632</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19733023e-07</v>
+        <v>0.000967116911075</v>
       </c>
       <c r="W28" t="n">
-        <v>27.658867</v>
+        <v>34.68658</v>
       </c>
       <c r="X28" t="n">
-        <v>0.122654806207709</v>
+        <v>0.133313640973085</v>
       </c>
       <c r="Y28" t="n">
-        <v>149.567041</v>
+        <v>75.19485899999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.663263481794662</v>
+        <v>0.289002272225966</v>
       </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>58.26023043585568</v>
+        <v>60.53524547926242</v>
       </c>
     </row>
     <row r="29">
@@ -3190,46 +3196,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12716.369465</v>
+        <v>13137.780857</v>
       </c>
       <c r="E29" t="n">
-        <v>250.024</v>
+        <v>246.141</v>
       </c>
       <c r="F29" t="n">
-        <v>1.10708674938281</v>
+        <v>1.091526151623337</v>
       </c>
       <c r="G29" t="n">
-        <v>12097.506842</v>
+        <v>12358.591255</v>
       </c>
       <c r="H29" t="n">
-        <v>53.56681568707835</v>
+        <v>54.80487018439013</v>
       </c>
       <c r="I29" t="n">
-        <v>3949.789703</v>
+        <v>3146.95806</v>
       </c>
       <c r="J29" t="n">
-        <v>17.48936039356207</v>
+        <v>13.95536306650189</v>
       </c>
       <c r="K29" t="n">
-        <v>298.950459</v>
+        <v>232.819909</v>
       </c>
       <c r="L29" t="n">
-        <v>1.323729289511443</v>
+        <v>1.032453022016102</v>
       </c>
       <c r="M29" t="n">
-        <v>7848.76668</v>
+        <v>8978.813286000001</v>
       </c>
       <c r="N29" t="n">
-        <v>34.75372600400484</v>
+        <v>39.81705409587214</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3238,41 +3244,41 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>368.838623</v>
+        <v>533.048602</v>
       </c>
       <c r="R29" t="n">
-        <v>1.633188622627834</v>
+        <v>2.363834099842203</v>
       </c>
       <c r="S29" t="n">
-        <v>181.12779</v>
+        <v>355.822667</v>
       </c>
       <c r="T29" t="n">
-        <v>0.802019711123701</v>
+        <v>1.577915692106809</v>
       </c>
       <c r="U29" t="n">
-        <v>0.015693</v>
+        <v>2.7e-05</v>
       </c>
       <c r="V29" t="n">
-        <v>6.9487378644e-05</v>
+        <v>1.19733023e-07</v>
       </c>
       <c r="W29" t="n">
-        <v>27.844295</v>
+        <v>27.658867</v>
       </c>
       <c r="X29" t="n">
-        <v>0.123292364094671</v>
+        <v>0.122654806207709</v>
       </c>
       <c r="Y29" t="n">
-        <v>159.850845</v>
+        <v>149.567041</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.7078070600308179</v>
+        <v>0.663263481794662</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>56.30709105908899</v>
+        <v>58.26023043585568</v>
       </c>
     </row>
     <row r="30">
@@ -3283,46 +3289,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12853.42406</v>
+        <v>12716.369465</v>
       </c>
       <c r="E30" t="n">
-        <v>273.611</v>
+        <v>250.024</v>
       </c>
       <c r="F30" t="n">
-        <v>1.209427605319351</v>
+        <v>1.10708674938281</v>
       </c>
       <c r="G30" t="n">
-        <v>12175.777142</v>
+        <v>12097.506842</v>
       </c>
       <c r="H30" t="n">
-        <v>53.81991583580758</v>
+        <v>53.56681568707835</v>
       </c>
       <c r="I30" t="n">
-        <v>3794.1105</v>
+        <v>3949.789703</v>
       </c>
       <c r="J30" t="n">
-        <v>16.77089728238998</v>
+        <v>17.48936039356207</v>
       </c>
       <c r="K30" t="n">
-        <v>307.109411</v>
+        <v>298.950459</v>
       </c>
       <c r="L30" t="n">
-        <v>1.357498783004946</v>
+        <v>1.323729289511443</v>
       </c>
       <c r="M30" t="n">
-        <v>8074.557231</v>
+        <v>7848.76668</v>
       </c>
       <c r="N30" t="n">
-        <v>35.69151977041266</v>
+        <v>34.75372600400484</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3331,41 +3337,41 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>404.035918</v>
+        <v>368.838623</v>
       </c>
       <c r="R30" t="n">
-        <v>1.785937673447871</v>
+        <v>1.633188622627834</v>
       </c>
       <c r="S30" t="n">
-        <v>213.33052</v>
+        <v>181.12779</v>
       </c>
       <c r="T30" t="n">
-        <v>0.942973125879924</v>
+        <v>0.802019711123701</v>
       </c>
       <c r="U30" t="n">
-        <v>0.126898</v>
+        <v>0.015693</v>
       </c>
       <c r="V30" t="n">
-        <v>0.00056092022711</v>
+        <v>6.9487378644e-05</v>
       </c>
       <c r="W30" t="n">
-        <v>29.930766</v>
+        <v>27.844295</v>
       </c>
       <c r="X30" t="n">
-        <v>0.132301313356385</v>
+        <v>0.123292364094671</v>
       </c>
       <c r="Y30" t="n">
-        <v>160.647734</v>
+        <v>159.850845</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.710102313984453</v>
+        <v>0.7078070600308179</v>
       </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>56.81528111457482</v>
+        <v>56.30709105908899</v>
       </c>
     </row>
     <row r="31">
@@ -3376,46 +3382,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12403.274809</v>
+        <v>12853.42406</v>
       </c>
       <c r="E31" t="n">
-        <v>243.868</v>
+        <v>273.611</v>
       </c>
       <c r="F31" t="n">
-        <v>1.242971912382535</v>
+        <v>1.209427605319351</v>
       </c>
       <c r="G31" t="n">
-        <v>11810.666658</v>
+        <v>12175.777142</v>
       </c>
       <c r="H31" t="n">
-        <v>60.19784031692107</v>
+        <v>53.81991583580758</v>
       </c>
       <c r="I31" t="n">
-        <v>3468.63226</v>
+        <v>3794.1105</v>
       </c>
       <c r="J31" t="n">
-        <v>17.67928745700114</v>
+        <v>16.77089728238998</v>
       </c>
       <c r="K31" t="n">
-        <v>267.477167</v>
+        <v>307.109411</v>
       </c>
       <c r="L31" t="n">
-        <v>1.36330558246532</v>
+        <v>1.357498783004946</v>
       </c>
       <c r="M31" t="n">
         <v>8074.557231</v>
       </c>
       <c r="N31" t="n">
-        <v>41.15524727745461</v>
+        <v>35.69151977041266</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3424,41 +3430,41 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>348.740151</v>
+        <v>404.035918</v>
       </c>
       <c r="R31" t="n">
-        <v>1.777495253223236</v>
+        <v>1.785937673447871</v>
       </c>
       <c r="S31" t="n">
-        <v>219.975987</v>
+        <v>213.33052</v>
       </c>
       <c r="T31" t="n">
-        <v>1.121196603242843</v>
+        <v>0.942973125879924</v>
       </c>
       <c r="U31" t="n">
-        <v>0.312924</v>
+        <v>0.126898</v>
       </c>
       <c r="V31" t="n">
-        <v>0.00159494375117</v>
+        <v>0.00056092022711</v>
       </c>
       <c r="W31" t="n">
-        <v>31.619406</v>
+        <v>29.930766</v>
       </c>
       <c r="X31" t="n">
-        <v>0.1611610934777</v>
+        <v>0.132301313356385</v>
       </c>
       <c r="Y31" t="n">
-        <v>96.831834</v>
+        <v>160.647734</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.493542612751522</v>
+        <v>0.710102313984453</v>
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>63.21830748252685</v>
+        <v>56.81528111457482</v>
       </c>
     </row>
     <row r="32">
@@ -3469,46 +3475,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13892.529244</v>
+        <v>12403.274809</v>
       </c>
       <c r="E32" t="n">
-        <v>265.988</v>
+        <v>243.868</v>
       </c>
       <c r="F32" t="n">
-        <v>1.167381161016077</v>
+        <v>1.242971912382535</v>
       </c>
       <c r="G32" t="n">
-        <v>13250.832416</v>
+        <v>11810.666658</v>
       </c>
       <c r="H32" t="n">
-        <v>58.15590225957391</v>
+        <v>60.19784031692107</v>
       </c>
       <c r="I32" t="n">
-        <v>4446.231878</v>
+        <v>3468.63226</v>
       </c>
       <c r="J32" t="n">
-        <v>19.51384021792837</v>
+        <v>17.67928745700114</v>
       </c>
       <c r="K32" t="n">
-        <v>303.187937</v>
+        <v>267.477167</v>
       </c>
       <c r="L32" t="n">
-        <v>1.330646066368141</v>
+        <v>1.36330558246532</v>
       </c>
       <c r="M32" t="n">
-        <v>8501.412601</v>
+        <v>8074.557231</v>
       </c>
       <c r="N32" t="n">
-        <v>37.31141597527739</v>
+        <v>41.15524727745461</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3517,41 +3523,41 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>375.708828</v>
+        <v>348.740151</v>
       </c>
       <c r="R32" t="n">
-        <v>1.64892930445971</v>
+        <v>1.777495253223236</v>
       </c>
       <c r="S32" t="n">
-        <v>231.098909</v>
+        <v>219.975987</v>
       </c>
       <c r="T32" t="n">
-        <v>1.014258209761225</v>
+        <v>1.121196603242843</v>
       </c>
       <c r="U32" t="n">
-        <v>0.529031</v>
+        <v>0.312924</v>
       </c>
       <c r="V32" t="n">
-        <v>0.002321837161802</v>
+        <v>0.00159494375117</v>
       </c>
       <c r="W32" t="n">
-        <v>37.957213</v>
+        <v>31.619406</v>
       </c>
       <c r="X32" t="n">
-        <v>0.16658847534804</v>
+        <v>0.1611610934777</v>
       </c>
       <c r="Y32" t="n">
-        <v>106.123675</v>
+        <v>96.831834</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.465760782188643</v>
+        <v>0.493542612751522</v>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>60.97221272504969</v>
+        <v>63.21830748252685</v>
       </c>
     </row>
     <row r="33">
@@ -3562,46 +3568,46 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/03</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14734.308723</v>
+        <v>13892.529244</v>
       </c>
       <c r="E33" t="n">
-        <v>225.881</v>
+        <v>265.988</v>
       </c>
       <c r="F33" t="n">
-        <v>0.967818173454301</v>
+        <v>1.167381161016077</v>
       </c>
       <c r="G33" t="n">
-        <v>14222.321126</v>
+        <v>13250.832416</v>
       </c>
       <c r="H33" t="n">
-        <v>60.9374885645355</v>
+        <v>58.15590225957391</v>
       </c>
       <c r="I33" t="n">
-        <v>5165.989955</v>
+        <v>4446.231878</v>
       </c>
       <c r="J33" t="n">
-        <v>22.13439360694954</v>
+        <v>19.51384021792837</v>
       </c>
       <c r="K33" t="n">
-        <v>296.327606</v>
+        <v>303.187937</v>
       </c>
       <c r="L33" t="n">
-        <v>1.269656334012183</v>
+        <v>1.330646066368141</v>
       </c>
       <c r="M33" t="n">
-        <v>8760.003565000001</v>
+        <v>8501.412601</v>
       </c>
       <c r="N33" t="n">
-        <v>37.53343862357378</v>
+        <v>37.31141597527739</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3610,203 +3616,227 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>286.106597</v>
+        <v>375.708828</v>
       </c>
       <c r="R33" t="n">
-        <v>1.225863016906096</v>
+        <v>1.64892930445971</v>
       </c>
       <c r="S33" t="n">
-        <v>203.99446</v>
+        <v>231.098909</v>
       </c>
       <c r="T33" t="n">
-        <v>0.874042286301179</v>
+        <v>1.014258209761225</v>
       </c>
       <c r="U33" t="n">
-        <v>0.417032</v>
+        <v>0.529031</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001786830891097</v>
+        <v>0.002321837161802</v>
       </c>
       <c r="W33" t="n">
-        <v>32.207174</v>
+        <v>37.957213</v>
       </c>
       <c r="X33" t="n">
-        <v>0.137996061257055</v>
+        <v>0.16658847534804</v>
       </c>
       <c r="Y33" t="n">
-        <v>49.487931</v>
+        <v>106.123675</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.212037838456765</v>
+        <v>0.465760782188643</v>
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
-        <v>63.1311697548959</v>
+        <v>60.97221272504969</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>民營電廠</t>
+          <t>台電</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/04</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5703.5111465</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+        <v>14734.308723</v>
+      </c>
+      <c r="E34" t="n">
+        <v>225.881</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.967818173454301</v>
+      </c>
       <c r="G34" t="n">
-        <v>4080.97618581</v>
+        <v>14222.321126</v>
       </c>
       <c r="H34" t="n">
-        <v>19.17985013236659</v>
+        <v>60.9374885645355</v>
       </c>
       <c r="I34" t="n">
-        <v>1494.669633</v>
+        <v>5165.989955</v>
       </c>
       <c r="J34" t="n">
-        <v>7.024677002041702</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+        <v>22.13439360694954</v>
+      </c>
+      <c r="K34" t="n">
+        <v>296.327606</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.269656334012183</v>
+      </c>
       <c r="M34" t="n">
-        <v>2586.30655281</v>
+        <v>8760.003565000001</v>
       </c>
       <c r="N34" t="n">
-        <v>12.15517313032489</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+        <v>37.53343862357378</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
-        <v>1622.53496069</v>
+        <v>286.106597</v>
       </c>
       <c r="R34" t="n">
-        <v>7.625620920986275</v>
+        <v>1.225863016906096</v>
       </c>
       <c r="S34" t="n">
-        <v>5.016203</v>
+        <v>203.99446</v>
       </c>
       <c r="T34" t="n">
-        <v>0.023575247047033</v>
+        <v>0.874042286301179</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36099</v>
+        <v>0.417032</v>
       </c>
       <c r="V34" t="n">
-        <v>0.00639640689951</v>
+        <v>0.001786830891097</v>
       </c>
       <c r="W34" t="n">
-        <v>312.27143371</v>
+        <v>32.207174</v>
       </c>
       <c r="X34" t="n">
-        <v>1.467619272075776</v>
+        <v>0.137996061257055</v>
       </c>
       <c r="Y34" t="n">
-        <v>1303.88633398</v>
+        <v>49.487931</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.128029994963958</v>
+        <v>0.212037838456765</v>
       </c>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>26.80547105335286</v>
+        <v>63.1311697548959</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>民營電廠</t>
+          <t>台電</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2026/05</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4598.23585989</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+        <v>14982.829893</v>
+      </c>
+      <c r="E35" t="n">
+        <v>235.492</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.931949694591043</v>
+      </c>
       <c r="G35" t="n">
-        <v>2923.96870261</v>
+        <v>14382.443185</v>
       </c>
       <c r="H35" t="n">
-        <v>14.54594165071788</v>
+        <v>56.91791455223012</v>
       </c>
       <c r="I35" t="n">
-        <v>949.59156</v>
+        <v>4969.529585</v>
       </c>
       <c r="J35" t="n">
-        <v>4.723957343129095</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+        <v>19.66670451226327</v>
+      </c>
+      <c r="K35" t="n">
+        <v>258.306727</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.022238018015312</v>
+      </c>
       <c r="M35" t="n">
-        <v>1974.37714261</v>
+        <v>9154.606873000001</v>
       </c>
       <c r="N35" t="n">
-        <v>9.82198430758878</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+        <v>36.22897202195153</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
-        <v>1674.26715728</v>
+        <v>364.894708</v>
       </c>
       <c r="R35" t="n">
-        <v>8.329019512339316</v>
+        <v>1.444055473979956</v>
       </c>
       <c r="S35" t="n">
-        <v>16.980623</v>
+        <v>265.956997</v>
       </c>
       <c r="T35" t="n">
-        <v>0.08447393815479699</v>
+        <v>1.052513640074826</v>
       </c>
       <c r="U35" t="n">
-        <v>1.09834</v>
+        <v>0.347977</v>
       </c>
       <c r="V35" t="n">
-        <v>0.005463939999901</v>
+        <v>0.001377104355455</v>
       </c>
       <c r="W35" t="n">
-        <v>300.17489111</v>
+        <v>42.349854</v>
       </c>
       <c r="X35" t="n">
-        <v>1.493287683687986</v>
+        <v>0.16759776765782</v>
       </c>
       <c r="Y35" t="n">
-        <v>1356.01330317</v>
+        <v>56.23988</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.745793950496635</v>
+        <v>0.222566961891856</v>
       </c>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>22.87496116305719</v>
+        <v>59.29391972080111</v>
       </c>
     </row>
     <row r="36">
@@ -3817,77 +3847,77 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5905.64578929</v>
+        <v>5703.5111465</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>4090.89500397</v>
+        <v>4080.97618581</v>
       </c>
       <c r="H36" t="n">
-        <v>18.07070956084297</v>
+        <v>19.17985013236659</v>
       </c>
       <c r="I36" t="n">
-        <v>1460.299722</v>
+        <v>1494.669633</v>
       </c>
       <c r="J36" t="n">
-        <v>6.450581626375873</v>
+        <v>7.024677002041702</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>2630.59528197</v>
+        <v>2586.30655281</v>
       </c>
       <c r="N36" t="n">
-        <v>11.6201279344671</v>
+        <v>12.15517313032489</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>1814.75078532</v>
+        <v>1622.53496069</v>
       </c>
       <c r="R36" t="n">
-        <v>8.01629822691727</v>
+        <v>7.625620920986275</v>
       </c>
       <c r="S36" t="n">
-        <v>12.541678</v>
+        <v>5.016203</v>
       </c>
       <c r="T36" t="n">
-        <v>0.055400351346997</v>
+        <v>0.023575247047033</v>
       </c>
       <c r="U36" t="n">
-        <v>1.28194</v>
+        <v>1.36099</v>
       </c>
       <c r="V36" t="n">
-        <v>0.005662713267377</v>
+        <v>0.00639640689951</v>
       </c>
       <c r="W36" t="n">
-        <v>413.98667443</v>
+        <v>312.27143371</v>
       </c>
       <c r="X36" t="n">
-        <v>1.828703241814771</v>
+        <v>1.467619272075776</v>
       </c>
       <c r="Y36" t="n">
-        <v>1386.94049289</v>
+        <v>1303.88633398</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.126531920488123</v>
+        <v>6.128029994963958</v>
       </c>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>26.08700778776024</v>
+        <v>26.80547105335286</v>
       </c>
     </row>
     <row r="37">
@@ -3898,77 +3928,77 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4975.86877575</v>
+        <v>4598.23585989</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>3847.17282962</v>
+        <v>2923.96870261</v>
       </c>
       <c r="H37" t="n">
-        <v>17.04440624774986</v>
+        <v>14.54594165071788</v>
       </c>
       <c r="I37" t="n">
-        <v>1108.12623</v>
+        <v>949.59156</v>
       </c>
       <c r="J37" t="n">
-        <v>4.909411267539306</v>
+        <v>4.723957343129095</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>2739.04659962</v>
+        <v>1974.37714261</v>
       </c>
       <c r="N37" t="n">
-        <v>12.13499498021056</v>
+        <v>9.82198430758878</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
-        <v>1128.69594613</v>
+        <v>1674.26715728</v>
       </c>
       <c r="R37" t="n">
-        <v>5.000542759065056</v>
+        <v>8.329019512339316</v>
       </c>
       <c r="S37" t="n">
-        <v>13.658556</v>
+        <v>16.980623</v>
       </c>
       <c r="T37" t="n">
-        <v>0.060512482160734</v>
+        <v>0.08447393815479699</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25209</v>
+        <v>1.09834</v>
       </c>
       <c r="V37" t="n">
-        <v>0.005547224303113</v>
+        <v>0.005463939999901</v>
       </c>
       <c r="W37" t="n">
-        <v>446.41242004</v>
+        <v>300.17489111</v>
       </c>
       <c r="X37" t="n">
-        <v>1.977773024029821</v>
+        <v>1.493287683687986</v>
       </c>
       <c r="Y37" t="n">
-        <v>667.37288009</v>
+        <v>1356.01330317</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.956710028571387</v>
+        <v>6.745793950496635</v>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>22.04494900681492</v>
+        <v>22.87496116305719</v>
       </c>
     </row>
     <row r="38">
@@ -3979,77 +4009,77 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5290.29863492</v>
+        <v>5905.64578929</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>4214.93074929</v>
+        <v>4090.89500397</v>
       </c>
       <c r="H38" t="n">
-        <v>16.87003493293413</v>
+        <v>18.07070956084297</v>
       </c>
       <c r="I38" t="n">
-        <v>1343.742459</v>
+        <v>1460.299722</v>
       </c>
       <c r="J38" t="n">
-        <v>5.378257336260001</v>
+        <v>6.450581626375873</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>2871.18829029</v>
+        <v>2630.59528197</v>
       </c>
       <c r="N38" t="n">
-        <v>11.49177759667412</v>
+        <v>11.6201279344671</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
-        <v>1075.36788563</v>
+        <v>1814.75078532</v>
       </c>
       <c r="R38" t="n">
-        <v>4.304102457528993</v>
+        <v>8.01629822691727</v>
       </c>
       <c r="S38" t="n">
-        <v>13.950592</v>
+        <v>12.541678</v>
       </c>
       <c r="T38" t="n">
-        <v>0.055836498479781</v>
+        <v>0.055400351346997</v>
       </c>
       <c r="U38" t="n">
-        <v>1.30091</v>
+        <v>1.28194</v>
       </c>
       <c r="V38" t="n">
-        <v>0.005206822709555</v>
+        <v>0.005662713267377</v>
       </c>
       <c r="W38" t="n">
-        <v>490.55057559</v>
+        <v>413.98667443</v>
       </c>
       <c r="X38" t="n">
-        <v>1.963402446877272</v>
+        <v>1.828703241814771</v>
       </c>
       <c r="Y38" t="n">
-        <v>569.56580804</v>
+        <v>1386.94049289</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.279656689462385</v>
+        <v>6.126531920488123</v>
       </c>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>21.17413739046312</v>
+        <v>26.08700778776024</v>
       </c>
     </row>
     <row r="39">
@@ -4060,77 +4090,77 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5816.22919</v>
+        <v>4975.86877575</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>4893.5689464</v>
+        <v>3847.17282962</v>
       </c>
       <c r="H39" t="n">
-        <v>18.78116590866005</v>
+        <v>17.04440624774986</v>
       </c>
       <c r="I39" t="n">
-        <v>1396.771931</v>
+        <v>1108.12623</v>
       </c>
       <c r="J39" t="n">
-        <v>5.360710283231836</v>
+        <v>4.909411267539306</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>3496.7970154</v>
+        <v>2739.04659962</v>
       </c>
       <c r="N39" t="n">
-        <v>13.42045562542821</v>
+        <v>12.13499498021056</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>922.6602435999999</v>
+        <v>1128.69594613</v>
       </c>
       <c r="R39" t="n">
-        <v>3.541103702058651</v>
+        <v>5.000542759065056</v>
       </c>
       <c r="S39" t="n">
-        <v>13.306576</v>
+        <v>13.658556</v>
       </c>
       <c r="T39" t="n">
-        <v>0.05106968232583</v>
+        <v>0.060512482160734</v>
       </c>
       <c r="U39" t="n">
-        <v>0.84632</v>
+        <v>1.25209</v>
       </c>
       <c r="V39" t="n">
-        <v>0.003248115333802</v>
+        <v>0.005547224303113</v>
       </c>
       <c r="W39" t="n">
-        <v>498.74942757</v>
+        <v>446.41242004</v>
       </c>
       <c r="X39" t="n">
-        <v>1.914164457196907</v>
+        <v>1.977773024029821</v>
       </c>
       <c r="Y39" t="n">
-        <v>409.75792003</v>
+        <v>667.37288009</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.572621447202113</v>
+        <v>2.956710028571387</v>
       </c>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
-        <v>22.3222696107187</v>
+        <v>22.04494900681492</v>
       </c>
     </row>
     <row r="40">
@@ -4141,77 +4171,77 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5972.9288043</v>
+        <v>5290.29863492</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>4878.30277984</v>
+        <v>4214.93074929</v>
       </c>
       <c r="H40" t="n">
-        <v>17.97466335825186</v>
+        <v>16.87003493293413</v>
       </c>
       <c r="I40" t="n">
-        <v>1764.22638</v>
+        <v>1343.742459</v>
       </c>
       <c r="J40" t="n">
-        <v>6.500493450160018</v>
+        <v>5.378257336260001</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>3114.07639984</v>
+        <v>2871.18829029</v>
       </c>
       <c r="N40" t="n">
-        <v>11.47416990809185</v>
+        <v>11.49177759667412</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>1094.62602446</v>
+        <v>1075.36788563</v>
       </c>
       <c r="R40" t="n">
-        <v>4.033274517965733</v>
+        <v>4.304102457528993</v>
       </c>
       <c r="S40" t="n">
-        <v>8.493983</v>
+        <v>13.950592</v>
       </c>
       <c r="T40" t="n">
-        <v>0.031297049790895</v>
+        <v>0.055836498479781</v>
       </c>
       <c r="U40" t="n">
-        <v>0.86927</v>
+        <v>1.30091</v>
       </c>
       <c r="V40" t="n">
-        <v>0.003202924525718</v>
+        <v>0.005206822709555</v>
       </c>
       <c r="W40" t="n">
-        <v>440.31156291</v>
+        <v>490.55057559</v>
       </c>
       <c r="X40" t="n">
-        <v>1.622378206773087</v>
+        <v>1.963402446877272</v>
       </c>
       <c r="Y40" t="n">
-        <v>644.95120855</v>
+        <v>569.56580804</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.376396336876032</v>
+        <v>2.279656689462385</v>
       </c>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>22.00793787621759</v>
+        <v>21.17413739046312</v>
       </c>
     </row>
     <row r="41">
@@ -4222,77 +4252,77 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5444.90428158</v>
+        <v>5816.22919</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>4610.94292511</v>
+        <v>4893.5689464</v>
       </c>
       <c r="H41" t="n">
-        <v>17.00999409478256</v>
+        <v>18.78116590866005</v>
       </c>
       <c r="I41" t="n">
-        <v>1750.26825</v>
+        <v>1396.771931</v>
       </c>
       <c r="J41" t="n">
-        <v>6.45682522649641</v>
+        <v>5.360710283231836</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>2860.67467511</v>
+        <v>3496.7970154</v>
       </c>
       <c r="N41" t="n">
-        <v>10.55316886828614</v>
+        <v>13.42045562542821</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
-        <v>833.9613564700001</v>
+        <v>922.6602435999999</v>
       </c>
       <c r="R41" t="n">
-        <v>3.076524255284103</v>
+        <v>3.541103702058651</v>
       </c>
       <c r="S41" t="n">
-        <v>13.862821</v>
+        <v>13.306576</v>
       </c>
       <c r="T41" t="n">
-        <v>0.051140625068874</v>
+        <v>0.05106968232583</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3293</v>
+        <v>0.84632</v>
       </c>
       <c r="V41" t="n">
-        <v>0.004903852751475</v>
+        <v>0.003248115333802</v>
       </c>
       <c r="W41" t="n">
-        <v>457.34907908</v>
+        <v>498.74942757</v>
       </c>
       <c r="X41" t="n">
-        <v>1.687183133853137</v>
+        <v>1.914164457196907</v>
       </c>
       <c r="Y41" t="n">
-        <v>361.42015639</v>
+        <v>409.75792003</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.333296643610618</v>
+        <v>1.572621447202113</v>
       </c>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
-        <v>20.08651835006665</v>
+        <v>22.3222696107187</v>
       </c>
     </row>
     <row r="42">
@@ -4303,77 +4333,77 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5262.96685564</v>
+        <v>5972.9288043</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>4644.82647434</v>
+        <v>4878.30277984</v>
       </c>
       <c r="H42" t="n">
-        <v>17.41204917196496</v>
+        <v>17.97466335825186</v>
       </c>
       <c r="I42" t="n">
-        <v>1610.77867</v>
+        <v>1764.22638</v>
       </c>
       <c r="J42" t="n">
-        <v>6.038321896875083</v>
+        <v>6.500493450160018</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>3034.04780434</v>
+        <v>3114.07639984</v>
       </c>
       <c r="N42" t="n">
-        <v>11.37372727508987</v>
+        <v>11.47416990809185</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
-        <v>618.1403812999999</v>
+        <v>1094.62602446</v>
       </c>
       <c r="R42" t="n">
-        <v>2.317221272706885</v>
+        <v>4.033274517965733</v>
       </c>
       <c r="S42" t="n">
-        <v>12.386979</v>
+        <v>8.493983</v>
       </c>
       <c r="T42" t="n">
-        <v>0.046435036622277</v>
+        <v>0.031297049790895</v>
       </c>
       <c r="U42" t="n">
-        <v>1.38969</v>
+        <v>0.86927</v>
       </c>
       <c r="V42" t="n">
-        <v>0.005209527362855</v>
+        <v>0.003202924525718</v>
       </c>
       <c r="W42" t="n">
-        <v>458.68854755</v>
+        <v>440.31156291</v>
       </c>
       <c r="X42" t="n">
-        <v>1.719484589721438</v>
+        <v>1.622378206773087</v>
       </c>
       <c r="Y42" t="n">
-        <v>145.67516475</v>
+        <v>644.95120855</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.546092119000316</v>
+        <v>2.376396336876032</v>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
-        <v>19.72927044467184</v>
+        <v>22.00793787621759</v>
       </c>
     </row>
     <row r="43">
@@ -4384,77 +4414,77 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5805.1610586</v>
+        <v>5444.90428158</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>4447.80894713</v>
+        <v>4610.94292511</v>
       </c>
       <c r="H43" t="n">
-        <v>17.09461137692342</v>
+        <v>17.00999409478256</v>
       </c>
       <c r="I43" t="n">
-        <v>1259.876349</v>
+        <v>1750.26825</v>
       </c>
       <c r="J43" t="n">
-        <v>4.842181133483534</v>
+        <v>6.45682522649641</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>3187.93259813</v>
+        <v>2860.67467511</v>
       </c>
       <c r="N43" t="n">
-        <v>12.25243024343989</v>
+        <v>10.55316886828614</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
-        <v>1357.35211147</v>
+        <v>833.9613564700001</v>
       </c>
       <c r="R43" t="n">
-        <v>5.21681734153585</v>
+        <v>3.076524255284103</v>
       </c>
       <c r="S43" t="n">
-        <v>11.838137</v>
+        <v>13.862821</v>
       </c>
       <c r="T43" t="n">
-        <v>0.045498436162003</v>
+        <v>0.051140625068874</v>
       </c>
       <c r="U43" t="n">
-        <v>1.21004</v>
+        <v>1.3293</v>
       </c>
       <c r="V43" t="n">
-        <v>0.004650641202536</v>
+        <v>0.004903852751475</v>
       </c>
       <c r="W43" t="n">
-        <v>436.65729578</v>
+        <v>457.34907908</v>
       </c>
       <c r="X43" t="n">
-        <v>1.678239075685558</v>
+        <v>1.687183133853137</v>
       </c>
       <c r="Y43" t="n">
-        <v>907.64663869</v>
+        <v>361.42015639</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.488429188485754</v>
+        <v>1.333296643610618</v>
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
-        <v>22.31142871845927</v>
+        <v>20.08651835006665</v>
       </c>
     </row>
     <row r="44">
@@ -4465,77 +4495,77 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5713.65967781</v>
+        <v>5262.96685564</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>3660.29172464</v>
+        <v>4644.82647434</v>
       </c>
       <c r="H44" t="n">
-        <v>16.23177016431657</v>
+        <v>17.41204917196496</v>
       </c>
       <c r="I44" t="n">
-        <v>1169.98751</v>
+        <v>1610.77867</v>
       </c>
       <c r="J44" t="n">
-        <v>5.188375623068364</v>
+        <v>6.038321896875083</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>2490.30421464</v>
+        <v>3034.04780434</v>
       </c>
       <c r="N44" t="n">
-        <v>11.0433945412482</v>
+        <v>11.37372727508987</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>2053.36795317</v>
+        <v>618.1403812999999</v>
       </c>
       <c r="R44" t="n">
-        <v>9.105776038085237</v>
+        <v>2.317221272706885</v>
       </c>
       <c r="S44" t="n">
-        <v>10.096836</v>
+        <v>12.386979</v>
       </c>
       <c r="T44" t="n">
-        <v>0.044774988899257</v>
+        <v>0.046435036622277</v>
       </c>
       <c r="U44" t="n">
-        <v>1.31856</v>
+        <v>1.38969</v>
       </c>
       <c r="V44" t="n">
-        <v>0.005847228712342</v>
+        <v>0.005209527362855</v>
       </c>
       <c r="W44" t="n">
-        <v>358.43795997</v>
+        <v>458.68854755</v>
       </c>
       <c r="X44" t="n">
-        <v>1.589513356335489</v>
+        <v>1.719484589721438</v>
       </c>
       <c r="Y44" t="n">
-        <v>1683.5145972</v>
+        <v>145.67516475</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.465640464138147</v>
+        <v>0.546092119000316</v>
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="n">
-        <v>25.3375462024018</v>
+        <v>19.72927044467184</v>
       </c>
     </row>
     <row r="45">
@@ -4546,77 +4576,77 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6210.3180455</v>
+        <v>5805.1610586</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>4073.98425523</v>
+        <v>4447.80894713</v>
       </c>
       <c r="H45" t="n">
-        <v>18.03928417335666</v>
+        <v>17.09461137692342</v>
       </c>
       <c r="I45" t="n">
-        <v>1202.13972</v>
+        <v>1259.876349</v>
       </c>
       <c r="J45" t="n">
-        <v>5.322980813516946</v>
+        <v>4.842181133483534</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>2871.84453523</v>
+        <v>3187.93259813</v>
       </c>
       <c r="N45" t="n">
-        <v>12.71630335983972</v>
+        <v>12.25243024343989</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>2136.33379027</v>
+        <v>1357.35211147</v>
       </c>
       <c r="R45" t="n">
-        <v>9.459519212022331</v>
+        <v>5.21681734153585</v>
       </c>
       <c r="S45" t="n">
-        <v>1.551418</v>
+        <v>11.838137</v>
       </c>
       <c r="T45" t="n">
-        <v>0.006869557764671</v>
+        <v>0.045498436162003</v>
       </c>
       <c r="U45" t="n">
-        <v>1.89345</v>
+        <v>1.21004</v>
       </c>
       <c r="V45" t="n">
-        <v>0.008384048753795</v>
+        <v>0.004650641202536</v>
       </c>
       <c r="W45" t="n">
-        <v>360.97084514</v>
+        <v>436.65729578</v>
       </c>
       <c r="X45" t="n">
-        <v>1.598350716603239</v>
+        <v>1.678239075685558</v>
       </c>
       <c r="Y45" t="n">
-        <v>1771.91807713</v>
+        <v>907.64663869</v>
       </c>
       <c r="Z45" t="n">
-        <v>7.845914888900626</v>
+        <v>3.488429188485754</v>
       </c>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="n">
-        <v>27.49880338537899</v>
+        <v>22.31142871845927</v>
       </c>
     </row>
     <row r="46">
@@ -4627,77 +4657,77 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6094.81340493</v>
+        <v>5713.65967781</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>4023.921915</v>
+        <v>3660.29172464</v>
       </c>
       <c r="H46" t="n">
-        <v>17.78671999901505</v>
+        <v>16.23177016431657</v>
       </c>
       <c r="I46" t="n">
-        <v>924.8215</v>
+        <v>1169.98751</v>
       </c>
       <c r="J46" t="n">
-        <v>4.087937444374861</v>
+        <v>5.188375623068364</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>3099.100415</v>
+        <v>2490.30421464</v>
       </c>
       <c r="N46" t="n">
-        <v>13.69878255464019</v>
+        <v>11.0433945412482</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>2070.89148993</v>
+        <v>2053.36795317</v>
       </c>
       <c r="R46" t="n">
-        <v>9.153847380194007</v>
+        <v>9.105776038085237</v>
       </c>
       <c r="S46" t="n">
-        <v>7.629006</v>
+        <v>10.096836</v>
       </c>
       <c r="T46" t="n">
-        <v>0.033722074249745</v>
+        <v>0.044774988899257</v>
       </c>
       <c r="U46" t="n">
-        <v>1.95546</v>
+        <v>1.31856</v>
       </c>
       <c r="V46" t="n">
-        <v>0.008643611934819001</v>
+        <v>0.005847228712342</v>
       </c>
       <c r="W46" t="n">
-        <v>334.64967293</v>
+        <v>358.43795997</v>
       </c>
       <c r="X46" t="n">
-        <v>1.479233483129822</v>
+        <v>1.589513356335489</v>
       </c>
       <c r="Y46" t="n">
-        <v>1726.657351</v>
+        <v>1683.5145972</v>
       </c>
       <c r="Z46" t="n">
-        <v>7.632248210879619</v>
+        <v>7.465640464138147</v>
       </c>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
-        <v>26.94056737920906</v>
+        <v>25.3375462024018</v>
       </c>
     </row>
     <row r="47">
@@ -4708,77 +4738,77 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3988.43562941</v>
+        <v>6210.3180455</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>2562.367762</v>
+        <v>4073.98425523</v>
       </c>
       <c r="H47" t="n">
-        <v>13.06014383748789</v>
+        <v>18.03928417335666</v>
       </c>
       <c r="I47" t="n">
-        <v>614.964887</v>
+        <v>1202.13972</v>
       </c>
       <c r="J47" t="n">
-        <v>3.13441731445905</v>
+        <v>5.322980813516946</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>1947.402875</v>
+        <v>2871.84453523</v>
       </c>
       <c r="N47" t="n">
-        <v>9.925726523028843</v>
+        <v>12.71630335983972</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>1426.06786741</v>
+        <v>2136.33379027</v>
       </c>
       <c r="R47" t="n">
-        <v>7.2685317644869</v>
+        <v>9.459519212022331</v>
       </c>
       <c r="S47" t="n">
-        <v>9.490926</v>
+        <v>1.551418</v>
       </c>
       <c r="T47" t="n">
-        <v>0.04837434366338</v>
+        <v>0.006869557764671</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36981</v>
+        <v>1.89345</v>
       </c>
       <c r="V47" t="n">
-        <v>0.006981790785592</v>
+        <v>0.008384048753795</v>
       </c>
       <c r="W47" t="n">
-        <v>358.11673211</v>
+        <v>360.97084514</v>
       </c>
       <c r="X47" t="n">
-        <v>1.825286791899514</v>
+        <v>1.598350716603239</v>
       </c>
       <c r="Y47" t="n">
-        <v>1057.0903993</v>
+        <v>1771.91807713</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.387888838138414</v>
+        <v>7.845914888900626</v>
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>20.32867560197479</v>
+        <v>27.49880338537899</v>
       </c>
     </row>
     <row r="48">
@@ -4789,77 +4819,77 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5040.14046034</v>
+        <v>6094.81340493</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>3361.256587</v>
+        <v>4023.921915</v>
       </c>
       <c r="H48" t="n">
-        <v>14.75204752471914</v>
+        <v>17.78671999901505</v>
       </c>
       <c r="I48" t="n">
-        <v>519.841</v>
+        <v>924.8215</v>
       </c>
       <c r="J48" t="n">
-        <v>2.281503639727199</v>
+        <v>4.087937444374861</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>2841.415587</v>
+        <v>3099.100415</v>
       </c>
       <c r="N48" t="n">
-        <v>12.47054388499194</v>
+        <v>13.69878255464019</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
-        <v>1678.88387334</v>
+        <v>2070.89148993</v>
       </c>
       <c r="R48" t="n">
-        <v>7.368367765729342</v>
+        <v>9.153847380194007</v>
       </c>
       <c r="S48" t="n">
-        <v>10.760263</v>
+        <v>7.629006</v>
       </c>
       <c r="T48" t="n">
-        <v>0.047225169232365</v>
+        <v>0.033722074249745</v>
       </c>
       <c r="U48" t="n">
-        <v>1.49123</v>
+        <v>1.95546</v>
       </c>
       <c r="V48" t="n">
-        <v>0.006544783256169</v>
+        <v>0.008643611934819001</v>
       </c>
       <c r="W48" t="n">
-        <v>440.82800634</v>
+        <v>334.64967293</v>
       </c>
       <c r="X48" t="n">
-        <v>1.934727543534263</v>
+        <v>1.479233483129822</v>
       </c>
       <c r="Y48" t="n">
-        <v>1225.804374</v>
+        <v>1726.657351</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.379870269706547</v>
+        <v>7.632248210879619</v>
       </c>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
-        <v>22.12041529044848</v>
+        <v>26.94056737920906</v>
       </c>
     </row>
     <row r="49">
@@ -4870,356 +4900,320 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4780.87626548</v>
+        <v>3988.43562941</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>3645.090201</v>
+        <v>2562.367762</v>
       </c>
       <c r="H49" t="n">
-        <v>15.61788968708299</v>
+        <v>13.06014383748789</v>
       </c>
       <c r="I49" t="n">
-        <v>573.1900000000001</v>
+        <v>614.964887</v>
       </c>
       <c r="J49" t="n">
-        <v>2.455911293301654</v>
+        <v>3.13441731445905</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>3071.900201</v>
+        <v>1947.402875</v>
       </c>
       <c r="N49" t="n">
-        <v>13.16197839378134</v>
+        <v>9.925726523028843</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
-        <v>1135.78606448</v>
+        <v>1426.06786741</v>
       </c>
       <c r="R49" t="n">
-        <v>4.866431414593893</v>
+        <v>7.2685317644869</v>
       </c>
       <c r="S49" t="n">
-        <v>4.197303</v>
+        <v>9.490926</v>
       </c>
       <c r="T49" t="n">
-        <v>0.017983921281092</v>
+        <v>0.04837434366338</v>
       </c>
       <c r="U49" t="n">
-        <v>1.59787</v>
+        <v>1.36981</v>
       </c>
       <c r="V49" t="n">
-        <v>0.006846293512148</v>
+        <v>0.006981790785592</v>
       </c>
       <c r="W49" t="n">
-        <v>394.56808948</v>
+        <v>358.11673211</v>
       </c>
       <c r="X49" t="n">
-        <v>1.690581180638863</v>
+        <v>1.825286791899514</v>
       </c>
       <c r="Y49" t="n">
-        <v>735.422802</v>
+        <v>1057.0903993</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.15102001916179</v>
+        <v>5.387888838138414</v>
       </c>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
-        <v>20.48432110167688</v>
+        <v>20.32867560197479</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/03</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3310.117399994</v>
+        <v>5040.14046034</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>2314.315225448</v>
+        <v>3361.256587</v>
       </c>
       <c r="H50" t="n">
-        <v>10.87686307445006</v>
+        <v>14.75204752471914</v>
       </c>
       <c r="I50" t="n">
-        <v>2147.105685185</v>
+        <v>519.841</v>
       </c>
       <c r="J50" t="n">
-        <v>10.0910084708144</v>
-      </c>
-      <c r="K50" t="n">
-        <v>50.385481982</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.236802654380108</v>
-      </c>
+        <v>2.281503639727199</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>116.824058281</v>
+        <v>2841.415587</v>
       </c>
       <c r="N50" t="n">
-        <v>0.549051949255545</v>
+        <v>12.47054388499194</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>995.8021745459999</v>
+        <v>1678.88387334</v>
       </c>
       <c r="R50" t="n">
-        <v>4.68009015482313</v>
+        <v>7.368367765729342</v>
       </c>
       <c r="S50" t="n">
-        <v>0.494578</v>
+        <v>10.760263</v>
       </c>
       <c r="T50" t="n">
-        <v>0.002324427168124</v>
+        <v>0.047225169232365</v>
       </c>
       <c r="U50" t="n">
-        <v>0.7950159999999999</v>
+        <v>1.49123</v>
       </c>
       <c r="V50" t="n">
-        <v>0.003736431441539</v>
+        <v>0.006544783256169</v>
       </c>
       <c r="W50" t="n">
-        <v>607.564724</v>
+        <v>440.82800634</v>
       </c>
       <c r="X50" t="n">
-        <v>2.855444340143768</v>
+        <v>1.934727543534263</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.011636</v>
+        <v>1225.804374</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.4687095925e-05</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>19.233884856</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.09039578086341001</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>367.70233569</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.728134488110364</v>
-      </c>
+        <v>5.379870269706547</v>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
-        <v>15.55695322927319</v>
+        <v>22.12041529044848</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2026/04</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3152.160858996</v>
+        <v>4780.87626548</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>2112.103545503</v>
+        <v>3645.090201</v>
       </c>
       <c r="H51" t="n">
-        <v>10.50713535536046</v>
+        <v>15.61788968708299</v>
       </c>
       <c r="I51" t="n">
-        <v>1955.281599316</v>
+        <v>573.1900000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>9.726989221528063</v>
-      </c>
-      <c r="K51" t="n">
-        <v>44.475244705</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.221252133719099</v>
-      </c>
+        <v>2.455911293301654</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>112.346701482</v>
+        <v>3071.900201</v>
       </c>
       <c r="N51" t="n">
-        <v>0.558894000113297</v>
+        <v>13.16197839378134</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
-        <v>1040.057313493</v>
+        <v>1135.78606448</v>
       </c>
       <c r="R51" t="n">
-        <v>5.173999633432269</v>
+        <v>4.866431414593893</v>
       </c>
       <c r="S51" t="n">
-        <v>0.757783</v>
+        <v>4.197303</v>
       </c>
       <c r="T51" t="n">
-        <v>0.003769762409586</v>
+        <v>0.017983921281092</v>
       </c>
       <c r="U51" t="n">
-        <v>0.712547</v>
+        <v>1.59787</v>
       </c>
       <c r="V51" t="n">
-        <v>0.003544725727106</v>
+        <v>0.006846293512148</v>
       </c>
       <c r="W51" t="n">
-        <v>700.756137</v>
+        <v>394.56808948</v>
       </c>
       <c r="X51" t="n">
-        <v>3.486069420334704</v>
+        <v>1.690581180638863</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.117873</v>
+        <v>735.422802</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.000586385818242</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>23.103078114</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0.11493147170086</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>314.609895379</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.56509786744177</v>
-      </c>
+        <v>3.15102001916179</v>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
-        <v>15.68113498879273</v>
+        <v>20.48432110167688</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2026/05</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3859.580818995</v>
+        <v>5826.88865631</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>2652.574231209</v>
+        <v>4508.066905</v>
       </c>
       <c r="H52" t="n">
-        <v>11.7172155418892</v>
+        <v>17.8404853468939</v>
       </c>
       <c r="I52" t="n">
-        <v>2464.210091587</v>
+        <v>1402.8762</v>
       </c>
       <c r="J52" t="n">
-        <v>10.88515467122791</v>
-      </c>
-      <c r="K52" t="n">
-        <v>55.321474143</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.244371535017565</v>
-      </c>
+        <v>5.551823612432875</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>133.042665479</v>
+        <v>3105.190705</v>
       </c>
       <c r="N52" t="n">
-        <v>0.587689335643734</v>
+        <v>12.28866173446102</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>1207.006587786</v>
+        <v>1318.82175131</v>
       </c>
       <c r="R52" t="n">
-        <v>5.331709922825699</v>
+        <v>5.219181663722669</v>
       </c>
       <c r="S52" t="n">
-        <v>1.116014</v>
+        <v>5.669157</v>
       </c>
       <c r="T52" t="n">
-        <v>0.004929768385711</v>
+        <v>0.022435450608677</v>
       </c>
       <c r="U52" t="n">
-        <v>0.756781</v>
+        <v>1.57867</v>
       </c>
       <c r="V52" t="n">
-        <v>0.003342928537372</v>
+        <v>0.006247520189051</v>
       </c>
       <c r="W52" t="n">
-        <v>863.595315</v>
+        <v>510.54988631</v>
       </c>
       <c r="X52" t="n">
-        <v>3.814759386472912</v>
+        <v>2.020479721689468</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.009842999999999999</v>
+        <v>801.024038</v>
       </c>
       <c r="Z52" t="n">
-        <v>4.3479481638e-05</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>24.704981935</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0.10912931102363</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>316.823652851</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.399505048924435</v>
-      </c>
+        <v>3.170018971235472</v>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="n">
-        <v>17.0489254647149</v>
+        <v>23.05966701061657</v>
       </c>
     </row>
     <row r="53">
@@ -5230,89 +5224,89 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3949.008767995</v>
+        <v>3310.117399994</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>2655.303323939</v>
+        <v>2314.315225448</v>
       </c>
       <c r="H53" t="n">
-        <v>11.76398112810731</v>
+        <v>10.87686307445006</v>
       </c>
       <c r="I53" t="n">
-        <v>2474.767863644</v>
+        <v>2147.105685185</v>
       </c>
       <c r="J53" t="n">
-        <v>10.96414190495069</v>
+        <v>10.0910084708144</v>
       </c>
       <c r="K53" t="n">
-        <v>55.192857294</v>
+        <v>50.385481982</v>
       </c>
       <c r="L53" t="n">
-        <v>0.244524881869146</v>
+        <v>0.236802654380108</v>
       </c>
       <c r="M53" t="n">
-        <v>125.342603001</v>
+        <v>116.824058281</v>
       </c>
       <c r="N53" t="n">
-        <v>0.555314341287468</v>
+        <v>0.549051949255545</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="n">
-        <v>1293.705444056</v>
+        <v>995.8021745459999</v>
       </c>
       <c r="R53" t="n">
-        <v>5.731596195431153</v>
+        <v>4.68009015482313</v>
       </c>
       <c r="S53" t="n">
-        <v>0.6560859999999999</v>
+        <v>0.494578</v>
       </c>
       <c r="T53" t="n">
-        <v>0.002906704952625</v>
+        <v>0.002324427168124</v>
       </c>
       <c r="U53" t="n">
-        <v>0.69015</v>
+        <v>0.7950159999999999</v>
       </c>
       <c r="V53" t="n">
-        <v>0.003057621139689</v>
+        <v>0.003736431441539</v>
       </c>
       <c r="W53" t="n">
-        <v>983.141517</v>
+        <v>607.564724</v>
       </c>
       <c r="X53" t="n">
-        <v>4.355682512041508</v>
+        <v>2.855444340143768</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.1628</v>
+        <v>0.011636</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.000721264538928</v>
+        <v>5.4687095925e-05</v>
       </c>
       <c r="AA53" t="n">
-        <v>21.545239307</v>
+        <v>19.233884856</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.095453421958631</v>
+        <v>0.09039578086341001</v>
       </c>
       <c r="AC53" t="n">
-        <v>287.509651749</v>
+        <v>367.70233569</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.273774670799772</v>
+        <v>1.728134488110364</v>
       </c>
       <c r="AE53" t="n">
-        <v>17.49557732353846</v>
+        <v>15.55695322927319</v>
       </c>
     </row>
     <row r="54">
@@ -5323,89 +5317,89 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4441.374873993</v>
+        <v>3152.160858996</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>3006.064947446</v>
+        <v>2112.103545503</v>
       </c>
       <c r="H54" t="n">
-        <v>12.0316142044861</v>
+        <v>10.50713535536046</v>
       </c>
       <c r="I54" t="n">
-        <v>2815.838541458</v>
+        <v>1955.281599316</v>
       </c>
       <c r="J54" t="n">
-        <v>11.27024318677137</v>
+        <v>9.726989221528063</v>
       </c>
       <c r="K54" t="n">
-        <v>66.29480847799999</v>
+        <v>44.475244705</v>
       </c>
       <c r="L54" t="n">
-        <v>0.265341425854845</v>
+        <v>0.221252133719099</v>
       </c>
       <c r="M54" t="n">
-        <v>123.93159751</v>
+        <v>112.346701482</v>
       </c>
       <c r="N54" t="n">
-        <v>0.496029591859893</v>
+        <v>0.558894000113297</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>1435.309926547</v>
+        <v>1040.057313493</v>
       </c>
       <c r="R54" t="n">
-        <v>5.744751228597001</v>
+        <v>5.173999633432269</v>
       </c>
       <c r="S54" t="n">
-        <v>1.396436</v>
+        <v>0.757783</v>
       </c>
       <c r="T54" t="n">
-        <v>0.005589160416354</v>
+        <v>0.003769762409586</v>
       </c>
       <c r="U54" t="n">
-        <v>0.37701</v>
+        <v>0.712547</v>
       </c>
       <c r="V54" t="n">
-        <v>0.001508962364598</v>
+        <v>0.003544725727106</v>
       </c>
       <c r="W54" t="n">
-        <v>1078.758217</v>
+        <v>700.756137</v>
       </c>
       <c r="X54" t="n">
-        <v>4.317672077541317</v>
+        <v>3.486069420334704</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.109295</v>
+        <v>0.117873</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.00043744739301</v>
+        <v>0.000586385818242</v>
       </c>
       <c r="AA54" t="n">
-        <v>23.469241859</v>
+        <v>23.103078114</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.09393438553587199</v>
+        <v>0.11493147170086</v>
       </c>
       <c r="AC54" t="n">
-        <v>331.199726688</v>
+        <v>314.609895379</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.325609195345849</v>
+        <v>1.56509786744177</v>
       </c>
       <c r="AE54" t="n">
-        <v>17.7763654330831</v>
+        <v>15.68113498879273</v>
       </c>
     </row>
     <row r="55">
@@ -5416,89 +5410,89 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4388.579665996</v>
+        <v>3859.580818995</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>2897.443596669</v>
+        <v>2652.574231209</v>
       </c>
       <c r="H55" t="n">
-        <v>11.1201802807045</v>
+        <v>11.7172155418892</v>
       </c>
       <c r="I55" t="n">
-        <v>2693.94720692</v>
+        <v>2464.210091587</v>
       </c>
       <c r="J55" t="n">
-        <v>10.3391757624171</v>
+        <v>10.88515467122791</v>
       </c>
       <c r="K55" t="n">
-        <v>65.227377601</v>
+        <v>55.321474143</v>
       </c>
       <c r="L55" t="n">
-        <v>0.250337987250065</v>
+        <v>0.244371535017565</v>
       </c>
       <c r="M55" t="n">
-        <v>138.269012148</v>
+        <v>133.042665479</v>
       </c>
       <c r="N55" t="n">
-        <v>0.530666531037336</v>
+        <v>0.587689335643734</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>1491.136069327</v>
+        <v>1207.006587786</v>
       </c>
       <c r="R55" t="n">
-        <v>5.72287306404867</v>
+        <v>5.331709922825699</v>
       </c>
       <c r="S55" t="n">
-        <v>1.237867</v>
+        <v>1.116014</v>
       </c>
       <c r="T55" t="n">
-        <v>0.004750844578773</v>
+        <v>0.004929768385711</v>
       </c>
       <c r="U55" t="n">
-        <v>1.233366</v>
+        <v>0.756781</v>
       </c>
       <c r="V55" t="n">
-        <v>0.004733570064266</v>
+        <v>0.003342928537372</v>
       </c>
       <c r="W55" t="n">
-        <v>1150.765022</v>
+        <v>863.595315</v>
       </c>
       <c r="X55" t="n">
-        <v>4.416553447349387</v>
+        <v>3.814759386472912</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.125543</v>
+        <v>0.009842999999999999</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.00048182501105</v>
+        <v>4.3479481638e-05</v>
       </c>
       <c r="AA55" t="n">
-        <v>21.390172139</v>
+        <v>24.704981935</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.082093943327987</v>
+        <v>0.10912931102363</v>
       </c>
       <c r="AC55" t="n">
-        <v>316.384099188</v>
+        <v>316.823652851</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.214259433717209</v>
+        <v>1.399505048924435</v>
       </c>
       <c r="AE55" t="n">
-        <v>16.84305334475317</v>
+        <v>17.0489254647149</v>
       </c>
     </row>
     <row r="56">
@@ -5509,89 +5503,89 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4424.497741994</v>
+        <v>3949.008767995</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>3002.199100199</v>
+        <v>2655.303323939</v>
       </c>
       <c r="H56" t="n">
-        <v>11.06194522888831</v>
+        <v>11.76398112810731</v>
       </c>
       <c r="I56" t="n">
-        <v>2790.579205647</v>
+        <v>2474.767863644</v>
       </c>
       <c r="J56" t="n">
-        <v>10.2822075750058</v>
+        <v>10.96414190495069</v>
       </c>
       <c r="K56" t="n">
-        <v>56.537998032</v>
+        <v>55.192857294</v>
       </c>
       <c r="L56" t="n">
-        <v>0.208320706491293</v>
+        <v>0.244524881869146</v>
       </c>
       <c r="M56" t="n">
-        <v>155.08189652</v>
+        <v>125.342603001</v>
       </c>
       <c r="N56" t="n">
-        <v>0.571416947391215</v>
+        <v>0.555314341287468</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>1422.298641795</v>
+        <v>1293.705444056</v>
       </c>
       <c r="R56" t="n">
-        <v>5.240621674163996</v>
+        <v>5.731596195431153</v>
       </c>
       <c r="S56" t="n">
-        <v>0.73847</v>
+        <v>0.6560859999999999</v>
       </c>
       <c r="T56" t="n">
-        <v>0.002720976997374</v>
+        <v>0.002906704952625</v>
       </c>
       <c r="U56" t="n">
-        <v>0.477957</v>
+        <v>0.69015</v>
       </c>
       <c r="V56" t="n">
-        <v>0.001761087116245</v>
+        <v>0.003057621139689</v>
       </c>
       <c r="W56" t="n">
-        <v>1067.027534</v>
+        <v>983.141517</v>
       </c>
       <c r="X56" t="n">
-        <v>3.931584730020529</v>
+        <v>4.355682512041508</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.054869</v>
+        <v>0.1628</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.000202171092758</v>
+        <v>0.000721264538928</v>
       </c>
       <c r="AA56" t="n">
-        <v>27.14025871</v>
+        <v>21.545239307</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.100001380763847</v>
+        <v>0.095453421958631</v>
       </c>
       <c r="AC56" t="n">
-        <v>326.859553085</v>
+        <v>287.509651749</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.204351328173243</v>
+        <v>1.273774670799772</v>
       </c>
       <c r="AE56" t="n">
-        <v>16.30256690305231</v>
+        <v>17.49557732353846</v>
       </c>
     </row>
     <row r="57">
@@ -5602,89 +5596,89 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4320.649265995</v>
+        <v>4441.374873993</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>2872.931780541</v>
+        <v>3006.064947446</v>
       </c>
       <c r="H57" t="n">
-        <v>10.59838593004265</v>
+        <v>12.0316142044861</v>
       </c>
       <c r="I57" t="n">
-        <v>2676.723632319</v>
+        <v>2815.838541458</v>
       </c>
       <c r="J57" t="n">
-        <v>9.874564469484273</v>
+        <v>11.27024318677137</v>
       </c>
       <c r="K57" t="n">
-        <v>71.82636332600001</v>
+        <v>66.29480847799999</v>
       </c>
       <c r="L57" t="n">
-        <v>0.264970969250464</v>
+        <v>0.265341425854845</v>
       </c>
       <c r="M57" t="n">
-        <v>124.381784896</v>
+        <v>123.93159751</v>
       </c>
       <c r="N57" t="n">
-        <v>0.458850491307914</v>
+        <v>0.496029591859893</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>1447.717485454</v>
+        <v>1435.309926547</v>
       </c>
       <c r="R57" t="n">
-        <v>5.340700650268515</v>
+        <v>5.744751228597001</v>
       </c>
       <c r="S57" t="n">
-        <v>1.972862</v>
+        <v>1.396436</v>
       </c>
       <c r="T57" t="n">
-        <v>0.007277984463237</v>
+        <v>0.005589160416354</v>
       </c>
       <c r="U57" t="n">
-        <v>0.496823</v>
+        <v>0.37701</v>
       </c>
       <c r="V57" t="n">
-        <v>0.001832804359848</v>
+        <v>0.001508962364598</v>
       </c>
       <c r="W57" t="n">
-        <v>1080.43869</v>
+        <v>1078.758217</v>
       </c>
       <c r="X57" t="n">
-        <v>3.985791200448693</v>
+        <v>4.317672077541317</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.071462</v>
+        <v>0.109295</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.00026362681511</v>
+        <v>0.00043744739301</v>
       </c>
       <c r="AA57" t="n">
-        <v>16.761473973</v>
+        <v>23.469241859</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.061833897736607</v>
+        <v>0.09393438553587199</v>
       </c>
       <c r="AC57" t="n">
-        <v>347.976174481</v>
+        <v>331.199726688</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.28370113644502</v>
+        <v>1.325609195345849</v>
       </c>
       <c r="AE57" t="n">
-        <v>15.93908658031117</v>
+        <v>17.7763654330831</v>
       </c>
     </row>
     <row r="58">
@@ -5695,89 +5689,89 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4489.323363995</v>
+        <v>4388.579665996</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>3033.653353456</v>
+        <v>2897.443596669</v>
       </c>
       <c r="H58" t="n">
-        <v>11.37224859806586</v>
+        <v>11.1201802807045</v>
       </c>
       <c r="I58" t="n">
-        <v>2793.318279846</v>
+        <v>2693.94720692</v>
       </c>
       <c r="J58" t="n">
-        <v>10.47130511986203</v>
+        <v>10.3391757624171</v>
       </c>
       <c r="K58" t="n">
-        <v>94.354244343</v>
+        <v>65.227377601</v>
       </c>
       <c r="L58" t="n">
-        <v>0.353705515407302</v>
+        <v>0.250337987250065</v>
       </c>
       <c r="M58" t="n">
-        <v>145.980829267</v>
+        <v>138.269012148</v>
       </c>
       <c r="N58" t="n">
-        <v>0.547237962796533</v>
+        <v>0.530666531037336</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>1455.670010539</v>
+        <v>1491.136069327</v>
       </c>
       <c r="R58" t="n">
-        <v>5.456866460282857</v>
+        <v>5.72287306404867</v>
       </c>
       <c r="S58" t="n">
-        <v>0.991319</v>
+        <v>1.237867</v>
       </c>
       <c r="T58" t="n">
-        <v>0.003716155009979</v>
+        <v>0.004750844578773</v>
       </c>
       <c r="U58" t="n">
-        <v>0.46002</v>
+        <v>1.233366</v>
       </c>
       <c r="V58" t="n">
-        <v>0.001724475802129</v>
+        <v>0.004733570064266</v>
       </c>
       <c r="W58" t="n">
-        <v>1102.241752</v>
+        <v>1150.765022</v>
       </c>
       <c r="X58" t="n">
-        <v>4.131970847833212</v>
+        <v>4.416553447349387</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.046212</v>
+        <v>0.125543</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.000173234806678</v>
+        <v>0.00048182501105</v>
       </c>
       <c r="AA58" t="n">
-        <v>24.662017269</v>
+        <v>21.390172139</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.092450441311415</v>
+        <v>0.082093943327987</v>
       </c>
       <c r="AC58" t="n">
-        <v>327.26869027</v>
+        <v>316.384099188</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.226831305519442</v>
+        <v>1.214259433717209</v>
       </c>
       <c r="AE58" t="n">
-        <v>16.82911505834872</v>
+        <v>16.84305334475317</v>
       </c>
     </row>
     <row r="59">
@@ -5788,89 +5782,89 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4463.08572299</v>
+        <v>4424.497741994</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>3056.727145405</v>
+        <v>3002.199100199</v>
       </c>
       <c r="H59" t="n">
-        <v>11.74815808347797</v>
+        <v>11.06194522888831</v>
       </c>
       <c r="I59" t="n">
-        <v>2851.84589551</v>
+        <v>2790.579205647</v>
       </c>
       <c r="J59" t="n">
-        <v>10.9607219802179</v>
+        <v>10.2822075750058</v>
       </c>
       <c r="K59" t="n">
-        <v>71.50566892499999</v>
+        <v>56.537998032</v>
       </c>
       <c r="L59" t="n">
-        <v>0.274823319987377</v>
+        <v>0.208320706491293</v>
       </c>
       <c r="M59" t="n">
-        <v>133.37558097</v>
+        <v>155.08189652</v>
       </c>
       <c r="N59" t="n">
-        <v>0.512612783272702</v>
+        <v>0.571416947391215</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>1406.358577585</v>
+        <v>1422.298641795</v>
       </c>
       <c r="R59" t="n">
-        <v>5.405167718800335</v>
+        <v>5.240621674163996</v>
       </c>
       <c r="S59" t="n">
-        <v>1.664189</v>
+        <v>0.73847</v>
       </c>
       <c r="T59" t="n">
-        <v>0.006396107510667</v>
+        <v>0.002720976997374</v>
       </c>
       <c r="U59" t="n">
-        <v>0.556748</v>
+        <v>0.477957</v>
       </c>
       <c r="V59" t="n">
-        <v>0.002139793054965</v>
+        <v>0.001761087116245</v>
       </c>
       <c r="W59" t="n">
-        <v>1067.055921</v>
+        <v>1067.027534</v>
       </c>
       <c r="X59" t="n">
-        <v>4.10109932862792</v>
+        <v>3.931584730020529</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.294876</v>
+        <v>0.054869</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.001133319952431</v>
+        <v>0.000202171092758</v>
       </c>
       <c r="AA59" t="n">
-        <v>25.305480999</v>
+        <v>27.14025871</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.097258530779106</v>
+        <v>0.100001380763847</v>
       </c>
       <c r="AC59" t="n">
-        <v>311.481362586</v>
+        <v>326.859553085</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.197140638875246</v>
+        <v>1.204351328173243</v>
       </c>
       <c r="AE59" t="n">
-        <v>17.15332580227831</v>
+        <v>16.30256690305231</v>
       </c>
     </row>
     <row r="60">
@@ -5881,89 +5875,89 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3698.729209995</v>
+        <v>4320.649265995</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>2525.399515776</v>
+        <v>2872.931780541</v>
       </c>
       <c r="H60" t="n">
-        <v>11.19902663419103</v>
+        <v>10.59838593004265</v>
       </c>
       <c r="I60" t="n">
-        <v>2355.130036339</v>
+        <v>2676.723632319</v>
       </c>
       <c r="J60" t="n">
-        <v>10.44395702112869</v>
+        <v>9.874564469484273</v>
       </c>
       <c r="K60" t="n">
-        <v>58.372883379</v>
+        <v>71.82636332600001</v>
       </c>
       <c r="L60" t="n">
-        <v>0.258857844706236</v>
+        <v>0.264970969250464</v>
       </c>
       <c r="M60" t="n">
-        <v>111.896596058</v>
+        <v>124.381784896</v>
       </c>
       <c r="N60" t="n">
-        <v>0.496211768356104</v>
+        <v>0.458850491307914</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>1173.329694219</v>
+        <v>1447.717485454</v>
       </c>
       <c r="R60" t="n">
-        <v>5.20319672755149</v>
+        <v>5.340700650268515</v>
       </c>
       <c r="S60" t="n">
-        <v>1.606897</v>
+        <v>1.972862</v>
       </c>
       <c r="T60" t="n">
-        <v>0.007125875406637</v>
+        <v>0.007277984463237</v>
       </c>
       <c r="U60" t="n">
-        <v>0.179824</v>
+        <v>0.496823</v>
       </c>
       <c r="V60" t="n">
-        <v>0.000797439673559</v>
+        <v>0.001832804359848</v>
       </c>
       <c r="W60" t="n">
-        <v>878.311339</v>
+        <v>1080.43869</v>
       </c>
       <c r="X60" t="n">
-        <v>3.894921186579277</v>
+        <v>3.985791200448693</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.506223</v>
+        <v>0.071462</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.002244874454289</v>
+        <v>0.00026362681511</v>
       </c>
       <c r="AA60" t="n">
-        <v>21.979498822</v>
+        <v>16.761473973</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.09746932759592</v>
+        <v>0.061833897736607</v>
       </c>
       <c r="AC60" t="n">
-        <v>270.745912397</v>
+        <v>347.976174481</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.200638023841808</v>
+        <v>1.28370113644502</v>
       </c>
       <c r="AE60" t="n">
-        <v>16.40222336174252</v>
+        <v>15.93908658031117</v>
       </c>
     </row>
     <row r="61">
@@ -5974,89 +5968,89 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3657.269901996</v>
+        <v>4489.323363995</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>2517.693528809</v>
+        <v>3033.653353456</v>
       </c>
       <c r="H61" t="n">
-        <v>11.14815035657093</v>
+        <v>11.37224859806586</v>
       </c>
       <c r="I61" t="n">
-        <v>2379.781789767</v>
+        <v>2793.318279846</v>
       </c>
       <c r="J61" t="n">
-        <v>10.53748794465152</v>
+        <v>10.47130511986203</v>
       </c>
       <c r="K61" t="n">
-        <v>34.630937411</v>
+        <v>94.354244343</v>
       </c>
       <c r="L61" t="n">
-        <v>0.153343086769364</v>
+        <v>0.353705515407302</v>
       </c>
       <c r="M61" t="n">
-        <v>103.280801631</v>
+        <v>145.980829267</v>
       </c>
       <c r="N61" t="n">
-        <v>0.457319325150044</v>
+        <v>0.547237962796533</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>1139.576373187</v>
+        <v>1455.670010539</v>
       </c>
       <c r="R61" t="n">
-        <v>5.045955198961089</v>
+        <v>5.456866460282857</v>
       </c>
       <c r="S61" t="n">
-        <v>2.019625</v>
+        <v>0.991319</v>
       </c>
       <c r="T61" t="n">
-        <v>0.008942741801676</v>
+        <v>0.003716155009979</v>
       </c>
       <c r="U61" t="n">
-        <v>0.051883</v>
+        <v>0.46002</v>
       </c>
       <c r="V61" t="n">
-        <v>0.000229733872821</v>
+        <v>0.001724475802129</v>
       </c>
       <c r="W61" t="n">
-        <v>782.0357299999999</v>
+        <v>1102.241752</v>
       </c>
       <c r="X61" t="n">
-        <v>3.462793148765368</v>
+        <v>4.131970847833212</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.5146500000000001</v>
+        <v>0.046212</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.002278830014598</v>
+        <v>0.000173234806678</v>
       </c>
       <c r="AA61" t="n">
-        <v>23.787486086</v>
+        <v>24.662017269</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.105329130991179</v>
+        <v>0.092450441311415</v>
       </c>
       <c r="AC61" t="n">
-        <v>331.166999101</v>
+        <v>327.26869027</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.466381613515446</v>
+        <v>1.226831305519442</v>
       </c>
       <c r="AE61" t="n">
-        <v>16.19410555553202</v>
+        <v>16.82911505834872</v>
       </c>
     </row>
     <row r="62">
@@ -6067,89 +6061,89 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3674.943847998</v>
+        <v>4463.08572299</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>2566.387030979</v>
+        <v>3056.727145405</v>
       </c>
       <c r="H62" t="n">
-        <v>11.34405897862137</v>
+        <v>11.74815808347797</v>
       </c>
       <c r="I62" t="n">
-        <v>2349.800331532</v>
+        <v>2851.84589551</v>
       </c>
       <c r="J62" t="n">
-        <v>10.38669274240934</v>
+        <v>10.9607219802179</v>
       </c>
       <c r="K62" t="n">
-        <v>35.645496538</v>
+        <v>71.50566892499999</v>
       </c>
       <c r="L62" t="n">
-        <v>0.15756182141205</v>
+        <v>0.274823319987377</v>
       </c>
       <c r="M62" t="n">
-        <v>180.941202909</v>
+        <v>133.37558097</v>
       </c>
       <c r="N62" t="n">
-        <v>0.79980441479997</v>
+        <v>0.512612783272702</v>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
-        <v>1108.556817019</v>
+        <v>1406.358577585</v>
       </c>
       <c r="R62" t="n">
-        <v>4.900092527594763</v>
+        <v>5.405167718800335</v>
       </c>
       <c r="S62" t="n">
-        <v>1.833322</v>
+        <v>1.664189</v>
       </c>
       <c r="T62" t="n">
-        <v>0.008103732073050001</v>
+        <v>0.006396107510667</v>
       </c>
       <c r="U62" t="n">
-        <v>0.029316</v>
+        <v>0.556748</v>
       </c>
       <c r="V62" t="n">
-        <v>0.00012958389713</v>
+        <v>0.002139793054965</v>
       </c>
       <c r="W62" t="n">
-        <v>737.150197</v>
+        <v>1067.055921</v>
       </c>
       <c r="X62" t="n">
-        <v>3.258384339512658</v>
+        <v>4.10109932862792</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.393627</v>
+        <v>0.294876</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.001739927707581</v>
+        <v>0.001133319952431</v>
       </c>
       <c r="AA62" t="n">
-        <v>23.890160716</v>
+        <v>25.305480999</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.105600359142894</v>
+        <v>0.097258530779106</v>
       </c>
       <c r="AC62" t="n">
-        <v>345.260194303</v>
+        <v>311.481362586</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.526134585261452</v>
+        <v>1.197140638875246</v>
       </c>
       <c r="AE62" t="n">
-        <v>16.24415150621613</v>
+        <v>17.15332580227831</v>
       </c>
     </row>
     <row r="63">
@@ -6160,89 +6154,89 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3228.041027458</v>
+        <v>3698.729209995</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>2101.863922731</v>
+        <v>2525.399515776</v>
       </c>
       <c r="H63" t="n">
-        <v>10.71299973594243</v>
+        <v>11.19902663419103</v>
       </c>
       <c r="I63" t="n">
-        <v>1938.225877779</v>
+        <v>2355.130036339</v>
       </c>
       <c r="J63" t="n">
-        <v>9.878952244379262</v>
+        <v>10.44395702112869</v>
       </c>
       <c r="K63" t="n">
-        <v>46.597120578</v>
+        <v>58.372883379</v>
       </c>
       <c r="L63" t="n">
-        <v>0.237501074664803</v>
+        <v>0.258857844706236</v>
       </c>
       <c r="M63" t="n">
-        <v>117.040924374</v>
+        <v>111.896596058</v>
       </c>
       <c r="N63" t="n">
-        <v>0.596546416898365</v>
+        <v>0.496211768356104</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
-        <v>1126.177104727</v>
+        <v>1173.329694219</v>
       </c>
       <c r="R63" t="n">
-        <v>5.740017179555931</v>
+        <v>5.20319672755149</v>
       </c>
       <c r="S63" t="n">
-        <v>1.157865</v>
+        <v>1.606897</v>
       </c>
       <c r="T63" t="n">
-        <v>0.005901527356319</v>
+        <v>0.007125875406637</v>
       </c>
       <c r="U63" t="n">
-        <v>0.021566</v>
+        <v>0.179824</v>
       </c>
       <c r="V63" t="n">
-        <v>0.000109919842958</v>
+        <v>0.000797439673559</v>
       </c>
       <c r="W63" t="n">
-        <v>765.92436746</v>
+        <v>878.311339</v>
       </c>
       <c r="X63" t="n">
-        <v>3.903843373309085</v>
+        <v>3.894921186579277</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.810688</v>
+        <v>0.506223</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.009228903858186</v>
+        <v>0.002244874454289</v>
       </c>
       <c r="AA63" t="n">
-        <v>24.07653597</v>
+        <v>21.979498822</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.122715805100209</v>
+        <v>0.09746932759592</v>
       </c>
       <c r="AC63" t="n">
-        <v>333.186082297</v>
+        <v>270.745912397</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.698217650089175</v>
+        <v>1.200638023841808</v>
       </c>
       <c r="AE63" t="n">
-        <v>16.45301691549836</v>
+        <v>16.40222336174252</v>
       </c>
     </row>
     <row r="64">
@@ -6253,89 +6247,89 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3852.347638966</v>
+        <v>3657.269901996</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>2449.7594017</v>
+        <v>2517.693528809</v>
       </c>
       <c r="H64" t="n">
-        <v>10.75162403780093</v>
+        <v>11.14815035657093</v>
       </c>
       <c r="I64" t="n">
-        <v>2236.407344782</v>
+        <v>2379.781789767</v>
       </c>
       <c r="J64" t="n">
-        <v>9.815254081599518</v>
+        <v>10.53748794465152</v>
       </c>
       <c r="K64" t="n">
-        <v>56.199006332</v>
+        <v>34.630937411</v>
       </c>
       <c r="L64" t="n">
-        <v>0.246648951305322</v>
+        <v>0.153343086769364</v>
       </c>
       <c r="M64" t="n">
-        <v>157.153050586</v>
+        <v>103.280801631</v>
       </c>
       <c r="N64" t="n">
-        <v>0.689721004896096</v>
+        <v>0.457319325150044</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
-        <v>1402.588237266</v>
+        <v>1139.576373187</v>
       </c>
       <c r="R64" t="n">
-        <v>6.155747946700886</v>
+        <v>5.045955198961089</v>
       </c>
       <c r="S64" t="n">
-        <v>1.754802</v>
+        <v>2.019625</v>
       </c>
       <c r="T64" t="n">
-        <v>0.007701560958063</v>
+        <v>0.008942741801676</v>
       </c>
       <c r="U64" t="n">
-        <v>0.192692</v>
+        <v>0.051883</v>
       </c>
       <c r="V64" t="n">
-        <v>0.000845696086585</v>
+        <v>0.000229733872821</v>
       </c>
       <c r="W64" t="n">
-        <v>1050.48050897</v>
+        <v>782.0357299999999</v>
       </c>
       <c r="X64" t="n">
-        <v>4.610400304472975</v>
+        <v>3.462793148765368</v>
       </c>
       <c r="Y64" t="n">
-        <v>3.365258</v>
+        <v>0.5146500000000001</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.014769609122061</v>
+        <v>0.002278830014598</v>
       </c>
       <c r="AA64" t="n">
-        <v>28.368082229</v>
+        <v>23.787486086</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.124503228597867</v>
+        <v>0.105329130991179</v>
       </c>
       <c r="AC64" t="n">
-        <v>318.426894067</v>
+        <v>331.166999101</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.397527547463335</v>
+        <v>1.466381613515446</v>
       </c>
       <c r="AE64" t="n">
-        <v>16.90737198450182</v>
+        <v>16.19410555553202</v>
       </c>
     </row>
     <row r="65">
@@ -6346,89 +6340,461 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3824.013033995</v>
+        <v>3674.943847998</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>2448.210127998</v>
+        <v>2566.387030979</v>
       </c>
       <c r="H65" t="n">
-        <v>10.48969260057883</v>
+        <v>11.34405897862137</v>
       </c>
       <c r="I65" t="n">
-        <v>2224.845165635</v>
+        <v>2349.800331532</v>
       </c>
       <c r="J65" t="n">
-        <v>9.532654736004794</v>
+        <v>10.38669274240934</v>
       </c>
       <c r="K65" t="n">
-        <v>47.749934909</v>
+        <v>35.645496538</v>
       </c>
       <c r="L65" t="n">
-        <v>0.204591155458804</v>
+        <v>0.15756182141205</v>
       </c>
       <c r="M65" t="n">
-        <v>175.615027454</v>
+        <v>180.941202909</v>
       </c>
       <c r="N65" t="n">
-        <v>0.75244670911523</v>
+        <v>0.79980441479997</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="n">
+        <v>1108.556817019</v>
+      </c>
+      <c r="R65" t="n">
+        <v>4.900092527594763</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1.833322</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.008103732073050001</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0.029316</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.00012958389713</v>
+      </c>
+      <c r="W65" t="n">
+        <v>737.150197</v>
+      </c>
+      <c r="X65" t="n">
+        <v>3.258384339512658</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0.393627</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.001739927707581</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>23.890160716</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.105600359142894</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>345.260194303</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.526134585261452</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>16.24415150621613</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>02月</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3228.041027458</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>2101.863922731</v>
+      </c>
+      <c r="H66" t="n">
+        <v>10.71299973594243</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1938.225877779</v>
+      </c>
+      <c r="J66" t="n">
+        <v>9.878952244379262</v>
+      </c>
+      <c r="K66" t="n">
+        <v>46.597120578</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.237501074664803</v>
+      </c>
+      <c r="M66" t="n">
+        <v>117.040924374</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.596546416898365</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="n">
+        <v>1126.177104727</v>
+      </c>
+      <c r="R66" t="n">
+        <v>5.740017179555931</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1.157865</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.005901527356319</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0.021566</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0.000109919842958</v>
+      </c>
+      <c r="W66" t="n">
+        <v>765.92436746</v>
+      </c>
+      <c r="X66" t="n">
+        <v>3.903843373309085</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.810688</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.009228903858186</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>24.07653597</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.122715805100209</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>333.186082297</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.698217650089175</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>16.45301691549836</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>03月</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>3852.347638966</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>2449.7594017</v>
+      </c>
+      <c r="H67" t="n">
+        <v>10.75162403780093</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2236.407344782</v>
+      </c>
+      <c r="J67" t="n">
+        <v>9.815254081599518</v>
+      </c>
+      <c r="K67" t="n">
+        <v>56.199006332</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.246648951305322</v>
+      </c>
+      <c r="M67" t="n">
+        <v>157.153050586</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.689721004896096</v>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="n">
+        <v>1402.588237266</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6.155747946700886</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1.754802</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.007701560958063</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.192692</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.000845696086585</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1050.48050897</v>
+      </c>
+      <c r="X67" t="n">
+        <v>4.610400304472975</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>3.365258</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.014769609122061</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>28.368082229</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.124503228597867</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>318.426894067</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.397527547463335</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>16.90737198450182</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>04月</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3824.013033995</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>2448.210127998</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10.48969260057883</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2224.845165635</v>
+      </c>
+      <c r="J68" t="n">
+        <v>9.532654736004794</v>
+      </c>
+      <c r="K68" t="n">
+        <v>47.749934909</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.204591155458804</v>
+      </c>
+      <c r="M68" t="n">
+        <v>175.615027454</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.75244670911523</v>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="n">
         <v>1375.802905997</v>
       </c>
-      <c r="R65" t="n">
+      <c r="R68" t="n">
         <v>5.894816542848387</v>
       </c>
-      <c r="S65" t="n">
+      <c r="S68" t="n">
         <v>0.825287</v>
       </c>
-      <c r="T65" t="n">
+      <c r="T68" t="n">
         <v>0.003536055520011</v>
       </c>
-      <c r="U65" t="n">
+      <c r="U68" t="n">
         <v>0.5118509999999999</v>
       </c>
-      <c r="V65" t="n">
+      <c r="V68" t="n">
         <v>0.00219309592175</v>
       </c>
-      <c r="W65" t="n">
+      <c r="W68" t="n">
         <v>1062.48103</v>
       </c>
-      <c r="X65" t="n">
+      <c r="X68" t="n">
         <v>4.552345924555163</v>
       </c>
-      <c r="Y65" t="n">
+      <c r="Y68" t="n">
         <v>0.568569</v>
       </c>
-      <c r="Z65" t="n">
+      <c r="Z68" t="n">
         <v>0.002436111984021</v>
       </c>
-      <c r="AA65" t="n">
+      <c r="AA68" t="n">
         <v>24.845848804</v>
       </c>
-      <c r="AB65" t="n">
+      <c r="AB68" t="n">
         <v>0.106455452239936</v>
       </c>
-      <c r="AC65" t="n">
+      <c r="AC68" t="n">
         <v>286.570320193</v>
       </c>
-      <c r="AD65" t="n">
+      <c r="AD68" t="n">
         <v>1.227849902627506</v>
       </c>
-      <c r="AE65" t="n">
+      <c r="AE68" t="n">
         <v>16.38450914342721</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>05月</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>4459.027324719</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>2813.571539247</v>
+      </c>
+      <c r="H69" t="n">
+        <v>11.13459113987435</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2607.57974388</v>
+      </c>
+      <c r="J69" t="n">
+        <v>10.31938726551541</v>
+      </c>
+      <c r="K69" t="n">
+        <v>51.527524898</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.203918014589555</v>
+      </c>
+      <c r="M69" t="n">
+        <v>154.464270469</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.611285859769388</v>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="n">
+        <v>1645.455785472</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6.511822128707959</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.068045</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.008184201187941</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.316157</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0.001251178042536</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1249.13984672</v>
+      </c>
+      <c r="X69" t="n">
+        <v>4.943418454351766</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.566299</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.006198562476382</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>25.254442649</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.099943395587971</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>367.110995103</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.452826337061364</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>17.64641326858231</v>
       </c>
     </row>
   </sheetData>
